--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N29"/>
+  <dimension ref="A1:N30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1942,6 +1942,58 @@
         </is>
       </c>
       <c r="N29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>23118.6</v>
+      </c>
+      <c r="D30" t="n">
+        <v>23118.6</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>23592.85</v>
+      </c>
+      <c r="G30" t="n">
+        <v>23434.76</v>
+      </c>
+      <c r="H30" t="n">
+        <v>158.09</v>
+      </c>
+      <c r="I30" t="n">
+        <v>23118.6</v>
+      </c>
+      <c r="J30" t="n">
+        <v>22960.51</v>
+      </c>
+      <c r="K30" t="n">
+        <v>158.09</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1956,7 +2008,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N29"/>
+  <dimension ref="A1:N30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3487,6 +3539,58 @@
         <v>0</v>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>55794.75</v>
+      </c>
+      <c r="D30" t="n">
+        <v>55794.75</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>56996.35</v>
+      </c>
+      <c r="G30" t="n">
+        <v>56595.81</v>
+      </c>
+      <c r="H30" t="n">
+        <v>400.54</v>
+      </c>
+      <c r="I30" t="n">
+        <v>55794.75</v>
+      </c>
+      <c r="J30" t="n">
+        <v>55394.21</v>
+      </c>
+      <c r="K30" t="n">
+        <v>400.54</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -1957,31 +1957,31 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>23118.6</v>
+        <v>23398.1</v>
       </c>
       <c r="D30" t="n">
         <v>23118.6</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>279.5</v>
       </c>
       <c r="F30" t="n">
-        <v>23592.85</v>
+        <v>23448.1</v>
       </c>
       <c r="G30" t="n">
         <v>23434.76</v>
       </c>
       <c r="H30" t="n">
-        <v>158.09</v>
+        <v>13.34</v>
       </c>
       <c r="I30" t="n">
-        <v>23118.6</v>
+        <v>23231.4</v>
       </c>
       <c r="J30" t="n">
         <v>22960.51</v>
       </c>
       <c r="K30" t="n">
-        <v>158.09</v>
+        <v>270.89</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
     </row>
   </sheetData>
@@ -3551,31 +3551,31 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>55794.75</v>
+        <v>56606.55</v>
       </c>
       <c r="D30" t="n">
         <v>55794.75</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>811.8</v>
       </c>
       <c r="F30" t="n">
-        <v>56996.35</v>
+        <v>56645.85</v>
       </c>
       <c r="G30" t="n">
         <v>56595.81</v>
       </c>
       <c r="H30" t="n">
-        <v>400.54</v>
+        <v>50.04</v>
       </c>
       <c r="I30" t="n">
-        <v>55794.75</v>
+        <v>55699.45</v>
       </c>
       <c r="J30" t="n">
         <v>55394.21</v>
       </c>
       <c r="K30" t="n">
-        <v>400.54</v>
+        <v>305.24</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N30"/>
+  <dimension ref="A1:N31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1995,6 +1995,58 @@
       </c>
       <c r="N30" t="n">
         <v>1.21</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>23217.6</v>
+      </c>
+      <c r="D31" t="n">
+        <v>23217.6</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>23284.75</v>
+      </c>
+      <c r="G31" t="n">
+        <v>23296.2</v>
+      </c>
+      <c r="H31" t="n">
+        <v>-11.45</v>
+      </c>
+      <c r="I31" t="n">
+        <v>23116.1</v>
+      </c>
+      <c r="J31" t="n">
+        <v>23127.55</v>
+      </c>
+      <c r="K31" t="n">
+        <v>-11.45</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2008,7 +2060,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N30"/>
+  <dimension ref="A1:N31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3591,6 +3643,58 @@
         <v>1.45</v>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>56292.45</v>
+      </c>
+      <c r="D31" t="n">
+        <v>56292.45</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>56368.7</v>
+      </c>
+      <c r="G31" t="n">
+        <v>56503.36</v>
+      </c>
+      <c r="H31" t="n">
+        <v>-134.66</v>
+      </c>
+      <c r="I31" t="n">
+        <v>55812.2</v>
+      </c>
+      <c r="J31" t="n">
+        <v>55946.86</v>
+      </c>
+      <c r="K31" t="n">
+        <v>-134.66</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -2009,31 +2009,31 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>23217.6</v>
+        <v>23118.6</v>
       </c>
       <c r="D31" t="n">
         <v>23217.6</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>-99</v>
       </c>
       <c r="F31" t="n">
-        <v>23284.75</v>
+        <v>23592.85</v>
       </c>
       <c r="G31" t="n">
         <v>23296.2</v>
       </c>
       <c r="H31" t="n">
-        <v>-11.45</v>
+        <v>296.65</v>
       </c>
       <c r="I31" t="n">
-        <v>23116.1</v>
+        <v>23118.6</v>
       </c>
       <c r="J31" t="n">
         <v>23127.55</v>
       </c>
       <c r="K31" t="n">
-        <v>-11.45</v>
+        <v>-8.949999999999999</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>0.43</v>
       </c>
     </row>
   </sheetData>
@@ -3655,31 +3655,31 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>56292.45</v>
+        <v>55794.75</v>
       </c>
       <c r="D31" t="n">
         <v>56292.45</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>-497.7</v>
       </c>
       <c r="F31" t="n">
-        <v>56368.7</v>
+        <v>56996.35</v>
       </c>
       <c r="G31" t="n">
         <v>56503.36</v>
       </c>
       <c r="H31" t="n">
-        <v>-134.66</v>
+        <v>492.99</v>
       </c>
       <c r="I31" t="n">
-        <v>55812.2</v>
+        <v>55794.75</v>
       </c>
       <c r="J31" t="n">
         <v>55946.86</v>
       </c>
       <c r="K31" t="n">
-        <v>-134.66</v>
+        <v>-152.11</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -3692,7 +3692,7 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>0.88</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N31"/>
+  <dimension ref="A1:N32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2047,6 +2047,58 @@
       </c>
       <c r="N31" t="n">
         <v>0.43</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>23270.6</v>
+      </c>
+      <c r="D32" t="n">
+        <v>23270.6</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>23363.55</v>
+      </c>
+      <c r="G32" t="n">
+        <v>23358.21</v>
+      </c>
+      <c r="H32" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="I32" t="n">
+        <v>23193.65</v>
+      </c>
+      <c r="J32" t="n">
+        <v>23188.31</v>
+      </c>
+      <c r="K32" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2060,7 +2112,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N31"/>
+  <dimension ref="A1:N32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3695,6 +3747,58 @@
         <v>0.88</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>56055.75</v>
+      </c>
+      <c r="D32" t="n">
+        <v>56055.75</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>56570.45</v>
+      </c>
+      <c r="G32" t="n">
+        <v>56404.64</v>
+      </c>
+      <c r="H32" t="n">
+        <v>165.81</v>
+      </c>
+      <c r="I32" t="n">
+        <v>56038.5</v>
+      </c>
+      <c r="J32" t="n">
+        <v>55872.69</v>
+      </c>
+      <c r="K32" t="n">
+        <v>165.81</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -2061,31 +2061,31 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>23270.6</v>
+        <v>23217.6</v>
       </c>
       <c r="D32" t="n">
         <v>23270.6</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>-53</v>
       </c>
       <c r="F32" t="n">
-        <v>23363.55</v>
+        <v>23284.75</v>
       </c>
       <c r="G32" t="n">
         <v>23358.21</v>
       </c>
       <c r="H32" t="n">
-        <v>5.34</v>
+        <v>-73.45999999999999</v>
       </c>
       <c r="I32" t="n">
-        <v>23193.65</v>
+        <v>23116.1</v>
       </c>
       <c r="J32" t="n">
         <v>23188.31</v>
       </c>
       <c r="K32" t="n">
-        <v>5.34</v>
+        <v>-72.20999999999999</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
     </row>
   </sheetData>
@@ -3759,31 +3759,31 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>56055.75</v>
+        <v>56292.45</v>
       </c>
       <c r="D32" t="n">
         <v>56055.75</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>236.7</v>
       </c>
       <c r="F32" t="n">
-        <v>56570.45</v>
+        <v>56368.7</v>
       </c>
       <c r="G32" t="n">
         <v>56404.64</v>
       </c>
       <c r="H32" t="n">
-        <v>165.81</v>
+        <v>-35.94</v>
       </c>
       <c r="I32" t="n">
-        <v>56038.5</v>
+        <v>55812.2</v>
       </c>
       <c r="J32" t="n">
         <v>55872.69</v>
       </c>
       <c r="K32" t="n">
-        <v>165.81</v>
+        <v>-60.49</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -3796,7 +3796,7 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>0.42</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N32"/>
+  <dimension ref="A1:N33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2099,6 +2099,58 @@
       </c>
       <c r="N32" t="n">
         <v>0.23</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>23346.4</v>
+      </c>
+      <c r="D33" t="n">
+        <v>23346.4</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
+        <v>23389.15</v>
+      </c>
+      <c r="G33" t="n">
+        <v>23394.84</v>
+      </c>
+      <c r="H33" t="n">
+        <v>-5.69</v>
+      </c>
+      <c r="I33" t="n">
+        <v>23286.6</v>
+      </c>
+      <c r="J33" t="n">
+        <v>23292.29</v>
+      </c>
+      <c r="K33" t="n">
+        <v>-5.69</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2112,7 +2164,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N32"/>
+  <dimension ref="A1:N33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3799,6 +3851,58 @@
         <v>0.42</v>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>56358.7</v>
+      </c>
+      <c r="D33" t="n">
+        <v>56358.7</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
+        <v>56497.45</v>
+      </c>
+      <c r="G33" t="n">
+        <v>56546.25</v>
+      </c>
+      <c r="H33" t="n">
+        <v>-48.8</v>
+      </c>
+      <c r="I33" t="n">
+        <v>56073.55</v>
+      </c>
+      <c r="J33" t="n">
+        <v>56122.35</v>
+      </c>
+      <c r="K33" t="n">
+        <v>-48.8</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -2113,31 +2113,31 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>23346.4</v>
+        <v>23270.6</v>
       </c>
       <c r="D33" t="n">
         <v>23346.4</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>-75.8</v>
       </c>
       <c r="F33" t="n">
-        <v>23389.15</v>
+        <v>23363.55</v>
       </c>
       <c r="G33" t="n">
         <v>23394.84</v>
       </c>
       <c r="H33" t="n">
-        <v>-5.69</v>
+        <v>-31.29</v>
       </c>
       <c r="I33" t="n">
-        <v>23286.6</v>
+        <v>23193.65</v>
       </c>
       <c r="J33" t="n">
         <v>23292.29</v>
       </c>
       <c r="K33" t="n">
-        <v>-5.69</v>
+        <v>-98.64</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>0.32</v>
       </c>
     </row>
   </sheetData>
@@ -3863,31 +3863,31 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>56358.7</v>
+        <v>56055.75</v>
       </c>
       <c r="D33" t="n">
         <v>56358.7</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>-302.95</v>
       </c>
       <c r="F33" t="n">
-        <v>56497.45</v>
+        <v>56570.45</v>
       </c>
       <c r="G33" t="n">
         <v>56546.25</v>
       </c>
       <c r="H33" t="n">
-        <v>-48.8</v>
+        <v>24.2</v>
       </c>
       <c r="I33" t="n">
-        <v>56073.55</v>
+        <v>56038.5</v>
       </c>
       <c r="J33" t="n">
         <v>56122.35</v>
       </c>
       <c r="K33" t="n">
-        <v>-48.8</v>
+        <v>-83.84999999999999</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -3900,7 +3900,7 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>0.54</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -2113,31 +2113,31 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>23270.6</v>
+        <v>23346.4</v>
       </c>
       <c r="D33" t="n">
         <v>23346.4</v>
       </c>
       <c r="E33" t="n">
-        <v>-75.8</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>23363.55</v>
+        <v>23389.15</v>
       </c>
       <c r="G33" t="n">
         <v>23394.84</v>
       </c>
       <c r="H33" t="n">
-        <v>-31.29</v>
+        <v>-5.69</v>
       </c>
       <c r="I33" t="n">
-        <v>23193.65</v>
+        <v>23286.6</v>
       </c>
       <c r="J33" t="n">
         <v>23292.29</v>
       </c>
       <c r="K33" t="n">
-        <v>-98.64</v>
+        <v>-5.69</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>0.32</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3863,31 +3863,31 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>56055.75</v>
+        <v>56358.7</v>
       </c>
       <c r="D33" t="n">
         <v>56358.7</v>
       </c>
       <c r="E33" t="n">
-        <v>-302.95</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>56570.45</v>
+        <v>56497.45</v>
       </c>
       <c r="G33" t="n">
         <v>56546.25</v>
       </c>
       <c r="H33" t="n">
-        <v>24.2</v>
+        <v>-48.8</v>
       </c>
       <c r="I33" t="n">
-        <v>56038.5</v>
+        <v>56073.55</v>
       </c>
       <c r="J33" t="n">
         <v>56122.35</v>
       </c>
       <c r="K33" t="n">
-        <v>-83.84999999999999</v>
+        <v>-48.8</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -3900,7 +3900,7 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>0.54</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N33"/>
+  <dimension ref="A1:N34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2150,6 +2150,58 @@
         </is>
       </c>
       <c r="N33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>23414.3</v>
+      </c>
+      <c r="D34" t="n">
+        <v>23414.3</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>23466.8</v>
+      </c>
+      <c r="G34" t="n">
+        <v>23482.46</v>
+      </c>
+      <c r="H34" t="n">
+        <v>-15.66</v>
+      </c>
+      <c r="I34" t="n">
+        <v>23314.8</v>
+      </c>
+      <c r="J34" t="n">
+        <v>23330.46</v>
+      </c>
+      <c r="K34" t="n">
+        <v>-15.66</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2164,7 +2216,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N33"/>
+  <dimension ref="A1:N34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3903,6 +3955,58 @@
         <v>0</v>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>56470.65</v>
+      </c>
+      <c r="D34" t="n">
+        <v>56470.65</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>56668.2</v>
+      </c>
+      <c r="G34" t="n">
+        <v>56669.39</v>
+      </c>
+      <c r="H34" t="n">
+        <v>-1.19</v>
+      </c>
+      <c r="I34" t="n">
+        <v>56269.55</v>
+      </c>
+      <c r="J34" t="n">
+        <v>56270.74</v>
+      </c>
+      <c r="K34" t="n">
+        <v>-1.19</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -2165,31 +2165,31 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>23414.3</v>
+        <v>23346.4</v>
       </c>
       <c r="D34" t="n">
         <v>23414.3</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>-67.90000000000001</v>
       </c>
       <c r="F34" t="n">
-        <v>23466.8</v>
+        <v>23389.15</v>
       </c>
       <c r="G34" t="n">
         <v>23482.46</v>
       </c>
       <c r="H34" t="n">
-        <v>-15.66</v>
+        <v>-93.31</v>
       </c>
       <c r="I34" t="n">
-        <v>23314.8</v>
+        <v>23286.6</v>
       </c>
       <c r="J34" t="n">
         <v>23330.46</v>
       </c>
       <c r="K34" t="n">
-        <v>-15.66</v>
+        <v>-43.86</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>0.29</v>
       </c>
     </row>
   </sheetData>
@@ -3967,31 +3967,31 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>56470.65</v>
+        <v>56358.7</v>
       </c>
       <c r="D34" t="n">
         <v>56470.65</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>-111.95</v>
       </c>
       <c r="F34" t="n">
-        <v>56668.2</v>
+        <v>56497.45</v>
       </c>
       <c r="G34" t="n">
         <v>56669.39</v>
       </c>
       <c r="H34" t="n">
-        <v>-1.19</v>
+        <v>-171.94</v>
       </c>
       <c r="I34" t="n">
-        <v>56269.55</v>
+        <v>56073.55</v>
       </c>
       <c r="J34" t="n">
         <v>56270.74</v>
       </c>
       <c r="K34" t="n">
-        <v>-1.19</v>
+        <v>-197.19</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -4004,7 +4004,7 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N34"/>
+  <dimension ref="A1:N35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2203,6 +2203,58 @@
       </c>
       <c r="N34" t="n">
         <v>0.29</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>23329</v>
+      </c>
+      <c r="D35" t="n">
+        <v>23329</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>23489</v>
+      </c>
+      <c r="G35" t="n">
+        <v>23450.09</v>
+      </c>
+      <c r="H35" t="n">
+        <v>38.91</v>
+      </c>
+      <c r="I35" t="n">
+        <v>23285.75</v>
+      </c>
+      <c r="J35" t="n">
+        <v>23246.84</v>
+      </c>
+      <c r="K35" t="n">
+        <v>38.91</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2216,7 +2268,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N34"/>
+  <dimension ref="A1:N35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4007,6 +4059,58 @@
         <v>0.2</v>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>56215.55</v>
+      </c>
+      <c r="D35" t="n">
+        <v>56215.55</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>56671.1</v>
+      </c>
+      <c r="G35" t="n">
+        <v>56555.45</v>
+      </c>
+      <c r="H35" t="n">
+        <v>115.65</v>
+      </c>
+      <c r="I35" t="n">
+        <v>56106.95</v>
+      </c>
+      <c r="J35" t="n">
+        <v>55991.3</v>
+      </c>
+      <c r="K35" t="n">
+        <v>115.65</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -2217,31 +2217,31 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>23329</v>
+        <v>23414.3</v>
       </c>
       <c r="D35" t="n">
         <v>23329</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>85.3</v>
       </c>
       <c r="F35" t="n">
-        <v>23489</v>
+        <v>23466.8</v>
       </c>
       <c r="G35" t="n">
         <v>23450.09</v>
       </c>
       <c r="H35" t="n">
-        <v>38.91</v>
+        <v>16.71</v>
       </c>
       <c r="I35" t="n">
-        <v>23285.75</v>
+        <v>23314.8</v>
       </c>
       <c r="J35" t="n">
         <v>23246.84</v>
       </c>
       <c r="K35" t="n">
-        <v>38.91</v>
+        <v>67.95999999999999</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>0.37</v>
       </c>
     </row>
   </sheetData>
@@ -4071,31 +4071,31 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>56215.55</v>
+        <v>56470.65</v>
       </c>
       <c r="D35" t="n">
         <v>56215.55</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>255.1</v>
       </c>
       <c r="F35" t="n">
-        <v>56671.1</v>
+        <v>56668.2</v>
       </c>
       <c r="G35" t="n">
         <v>56555.45</v>
       </c>
       <c r="H35" t="n">
-        <v>115.65</v>
+        <v>112.75</v>
       </c>
       <c r="I35" t="n">
-        <v>56106.95</v>
+        <v>56269.55</v>
       </c>
       <c r="J35" t="n">
         <v>55991.3</v>
       </c>
       <c r="K35" t="n">
-        <v>115.65</v>
+        <v>278.25</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N35"/>
+  <dimension ref="A1:N36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2255,6 +2255,58 @@
       </c>
       <c r="N35" t="n">
         <v>0.37</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>23446.8</v>
+      </c>
+      <c r="D36" t="n">
+        <v>23446.8</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>23466.9</v>
+      </c>
+      <c r="G36" t="n">
+        <v>23492.61</v>
+      </c>
+      <c r="H36" t="n">
+        <v>-25.71</v>
+      </c>
+      <c r="I36" t="n">
+        <v>23349.55</v>
+      </c>
+      <c r="J36" t="n">
+        <v>23375.26</v>
+      </c>
+      <c r="K36" t="n">
+        <v>-25.71</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2268,7 +2320,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N35"/>
+  <dimension ref="A1:N36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4111,6 +4163,58 @@
         <v>0.45</v>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>56548.9</v>
+      </c>
+      <c r="D36" t="n">
+        <v>56548.9</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>56623.8</v>
+      </c>
+      <c r="G36" t="n">
+        <v>56711.91</v>
+      </c>
+      <c r="H36" t="n">
+        <v>-88.11</v>
+      </c>
+      <c r="I36" t="n">
+        <v>56209.65</v>
+      </c>
+      <c r="J36" t="n">
+        <v>56297.76</v>
+      </c>
+      <c r="K36" t="n">
+        <v>-88.11</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -2269,31 +2269,31 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>23446.8</v>
+        <v>23414.3</v>
       </c>
       <c r="D36" t="n">
         <v>23446.8</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>-32.5</v>
       </c>
       <c r="F36" t="n">
-        <v>23466.9</v>
+        <v>23466.8</v>
       </c>
       <c r="G36" t="n">
         <v>23492.61</v>
       </c>
       <c r="H36" t="n">
-        <v>-25.71</v>
+        <v>-25.81</v>
       </c>
       <c r="I36" t="n">
-        <v>23349.55</v>
+        <v>23314.8</v>
       </c>
       <c r="J36" t="n">
         <v>23375.26</v>
       </c>
       <c r="K36" t="n">
-        <v>-25.71</v>
+        <v>-60.46</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
     </row>
   </sheetData>
@@ -4175,31 +4175,31 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>56548.9</v>
+        <v>56470.65</v>
       </c>
       <c r="D36" t="n">
         <v>56548.9</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>-78.25</v>
       </c>
       <c r="F36" t="n">
-        <v>56623.8</v>
+        <v>56668.2</v>
       </c>
       <c r="G36" t="n">
         <v>56711.91</v>
       </c>
       <c r="H36" t="n">
-        <v>-88.11</v>
+        <v>-43.71</v>
       </c>
       <c r="I36" t="n">
-        <v>56209.65</v>
+        <v>56269.55</v>
       </c>
       <c r="J36" t="n">
         <v>56297.76</v>
       </c>
       <c r="K36" t="n">
-        <v>-88.11</v>
+        <v>-28.21</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -4212,7 +4212,7 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N36"/>
+  <dimension ref="A1:N37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2307,6 +2307,58 @@
       </c>
       <c r="N36" t="n">
         <v>0.14</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>23063.1</v>
+      </c>
+      <c r="D37" t="n">
+        <v>23063.1</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>23281.95</v>
+      </c>
+      <c r="G37" t="n">
+        <v>23214.65</v>
+      </c>
+      <c r="H37" t="n">
+        <v>67.3</v>
+      </c>
+      <c r="I37" t="n">
+        <v>23046.15</v>
+      </c>
+      <c r="J37" t="n">
+        <v>22978.85</v>
+      </c>
+      <c r="K37" t="n">
+        <v>67.3</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2320,7 +2372,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N36"/>
+  <dimension ref="A1:N37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4215,6 +4267,58 @@
         <v>0.14</v>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>55438.5</v>
+      </c>
+      <c r="D37" t="n">
+        <v>55438.5</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>55918.4</v>
+      </c>
+      <c r="G37" t="n">
+        <v>55790.86</v>
+      </c>
+      <c r="H37" t="n">
+        <v>127.54</v>
+      </c>
+      <c r="I37" t="n">
+        <v>55341.2</v>
+      </c>
+      <c r="J37" t="n">
+        <v>55213.66</v>
+      </c>
+      <c r="K37" t="n">
+        <v>127.54</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -2321,31 +2321,31 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>23063.1</v>
+        <v>23446.8</v>
       </c>
       <c r="D37" t="n">
         <v>23063.1</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>383.7</v>
       </c>
       <c r="F37" t="n">
-        <v>23281.95</v>
+        <v>23466.9</v>
       </c>
       <c r="G37" t="n">
         <v>23214.65</v>
       </c>
       <c r="H37" t="n">
-        <v>67.3</v>
+        <v>252.25</v>
       </c>
       <c r="I37" t="n">
-        <v>23046.15</v>
+        <v>23349.55</v>
       </c>
       <c r="J37" t="n">
         <v>22978.85</v>
       </c>
       <c r="K37" t="n">
-        <v>67.3</v>
+        <v>370.7</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
     </row>
   </sheetData>
@@ -4279,31 +4279,31 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>55438.5</v>
+        <v>56548.9</v>
       </c>
       <c r="D37" t="n">
         <v>55438.5</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>1110.4</v>
       </c>
       <c r="F37" t="n">
-        <v>55918.4</v>
+        <v>56623.8</v>
       </c>
       <c r="G37" t="n">
         <v>55790.86</v>
       </c>
       <c r="H37" t="n">
-        <v>127.54</v>
+        <v>832.9400000000001</v>
       </c>
       <c r="I37" t="n">
-        <v>55341.2</v>
+        <v>56209.65</v>
       </c>
       <c r="J37" t="n">
         <v>55213.66</v>
       </c>
       <c r="K37" t="n">
-        <v>127.54</v>
+        <v>995.99</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -4316,7 +4316,7 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N37"/>
+  <dimension ref="A1:N38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2359,6 +2359,58 @@
       </c>
       <c r="N37" t="n">
         <v>1.66</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>23140.5</v>
+      </c>
+      <c r="D38" t="n">
+        <v>23140.5</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>23162.7</v>
+      </c>
+      <c r="G38" t="n">
+        <v>23195.15</v>
+      </c>
+      <c r="H38" t="n">
+        <v>-32.45</v>
+      </c>
+      <c r="I38" t="n">
+        <v>23020.95</v>
+      </c>
+      <c r="J38" t="n">
+        <v>23053.4</v>
+      </c>
+      <c r="K38" t="n">
+        <v>-32.45</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2372,7 +2424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N37"/>
+  <dimension ref="A1:N38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4319,6 +4371,58 @@
         <v>2</v>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>55580.4</v>
+      </c>
+      <c r="D38" t="n">
+        <v>55580.4</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>55762.6</v>
+      </c>
+      <c r="G38" t="n">
+        <v>55770.75</v>
+      </c>
+      <c r="H38" t="n">
+        <v>-8.15</v>
+      </c>
+      <c r="I38" t="n">
+        <v>55373.75</v>
+      </c>
+      <c r="J38" t="n">
+        <v>55381.9</v>
+      </c>
+      <c r="K38" t="n">
+        <v>-8.15</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -2373,31 +2373,31 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>23140.5</v>
+        <v>23063.1</v>
       </c>
       <c r="D38" t="n">
         <v>23140.5</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>-77.40000000000001</v>
       </c>
       <c r="F38" t="n">
-        <v>23162.7</v>
+        <v>23281.95</v>
       </c>
       <c r="G38" t="n">
         <v>23195.15</v>
       </c>
       <c r="H38" t="n">
-        <v>-32.45</v>
+        <v>86.8</v>
       </c>
       <c r="I38" t="n">
-        <v>23020.95</v>
+        <v>23046.15</v>
       </c>
       <c r="J38" t="n">
         <v>23053.4</v>
       </c>
       <c r="K38" t="n">
-        <v>-32.45</v>
+        <v>-7.25</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
     </row>
   </sheetData>
@@ -4383,31 +4383,31 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>55580.4</v>
+        <v>55438.5</v>
       </c>
       <c r="D38" t="n">
         <v>55580.4</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>-141.9</v>
       </c>
       <c r="F38" t="n">
-        <v>55762.6</v>
+        <v>55918.4</v>
       </c>
       <c r="G38" t="n">
         <v>55770.75</v>
       </c>
       <c r="H38" t="n">
-        <v>-8.15</v>
+        <v>147.65</v>
       </c>
       <c r="I38" t="n">
-        <v>55373.75</v>
+        <v>55341.2</v>
       </c>
       <c r="J38" t="n">
         <v>55381.9</v>
       </c>
       <c r="K38" t="n">
-        <v>-8.15</v>
+        <v>-40.7</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -4420,7 +4420,7 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>0.26</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -2373,31 +2373,31 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>23063.1</v>
+        <v>23140.5</v>
       </c>
       <c r="D38" t="n">
         <v>23140.5</v>
       </c>
       <c r="E38" t="n">
-        <v>-77.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>23281.95</v>
+        <v>23162.7</v>
       </c>
       <c r="G38" t="n">
         <v>23195.15</v>
       </c>
       <c r="H38" t="n">
-        <v>86.8</v>
+        <v>-32.45</v>
       </c>
       <c r="I38" t="n">
-        <v>23046.15</v>
+        <v>23020.95</v>
       </c>
       <c r="J38" t="n">
         <v>23053.4</v>
       </c>
       <c r="K38" t="n">
-        <v>-7.25</v>
+        <v>-32.45</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4383,31 +4383,31 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>55438.5</v>
+        <v>55580.4</v>
       </c>
       <c r="D38" t="n">
         <v>55580.4</v>
       </c>
       <c r="E38" t="n">
-        <v>-141.9</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>55918.4</v>
+        <v>55762.6</v>
       </c>
       <c r="G38" t="n">
         <v>55770.75</v>
       </c>
       <c r="H38" t="n">
-        <v>147.65</v>
+        <v>-8.15</v>
       </c>
       <c r="I38" t="n">
-        <v>55341.2</v>
+        <v>55373.75</v>
       </c>
       <c r="J38" t="n">
         <v>55381.9</v>
       </c>
       <c r="K38" t="n">
-        <v>-40.7</v>
+        <v>-8.15</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -4420,7 +4420,7 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>0.26</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N38"/>
+  <dimension ref="A1:N39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2410,6 +2410,58 @@
         </is>
       </c>
       <c r="N38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>22780.25</v>
+      </c>
+      <c r="D39" t="n">
+        <v>22780.25</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="n">
+        <v>23080.25</v>
+      </c>
+      <c r="G39" t="n">
+        <v>22986.26</v>
+      </c>
+      <c r="H39" t="n">
+        <v>93.98999999999999</v>
+      </c>
+      <c r="I39" t="n">
+        <v>22762.2</v>
+      </c>
+      <c r="J39" t="n">
+        <v>22668.21</v>
+      </c>
+      <c r="K39" t="n">
+        <v>93.98999999999999</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N39" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2424,7 +2476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N38"/>
+  <dimension ref="A1:N39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4423,6 +4475,58 @@
         <v>0</v>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>54471.65</v>
+      </c>
+      <c r="D39" t="n">
+        <v>54471.65</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="n">
+        <v>55390.1</v>
+      </c>
+      <c r="G39" t="n">
+        <v>55095.26</v>
+      </c>
+      <c r="H39" t="n">
+        <v>294.84</v>
+      </c>
+      <c r="I39" t="n">
+        <v>54437.7</v>
+      </c>
+      <c r="J39" t="n">
+        <v>54142.86</v>
+      </c>
+      <c r="K39" t="n">
+        <v>294.84</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -2425,31 +2425,31 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>22780.25</v>
+        <v>23140.5</v>
       </c>
       <c r="D39" t="n">
         <v>22780.25</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>360.25</v>
       </c>
       <c r="F39" t="n">
-        <v>23080.25</v>
+        <v>23162.7</v>
       </c>
       <c r="G39" t="n">
         <v>22986.26</v>
       </c>
       <c r="H39" t="n">
-        <v>93.98999999999999</v>
+        <v>176.44</v>
       </c>
       <c r="I39" t="n">
-        <v>22762.2</v>
+        <v>23020.95</v>
       </c>
       <c r="J39" t="n">
         <v>22668.21</v>
       </c>
       <c r="K39" t="n">
-        <v>93.98999999999999</v>
+        <v>352.74</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2462,7 +2462,7 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
     </row>
   </sheetData>
@@ -4487,31 +4487,31 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>54471.65</v>
+        <v>55580.4</v>
       </c>
       <c r="D39" t="n">
         <v>54471.65</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>1108.75</v>
       </c>
       <c r="F39" t="n">
-        <v>55390.1</v>
+        <v>55762.6</v>
       </c>
       <c r="G39" t="n">
         <v>55095.26</v>
       </c>
       <c r="H39" t="n">
-        <v>294.84</v>
+        <v>667.34</v>
       </c>
       <c r="I39" t="n">
-        <v>54437.7</v>
+        <v>55373.75</v>
       </c>
       <c r="J39" t="n">
         <v>54142.86</v>
       </c>
       <c r="K39" t="n">
-        <v>294.84</v>
+        <v>1230.89</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -4524,7 +4524,7 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N39"/>
+  <dimension ref="A1:N40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2463,6 +2463,58 @@
       </c>
       <c r="N39" t="n">
         <v>1.58</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>22716.2</v>
+      </c>
+      <c r="D40" t="n">
+        <v>22716.2</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="n">
+        <v>22753.25</v>
+      </c>
+      <c r="G40" t="n">
+        <v>22789.75</v>
+      </c>
+      <c r="H40" t="n">
+        <v>-36.5</v>
+      </c>
+      <c r="I40" t="n">
+        <v>22569.65</v>
+      </c>
+      <c r="J40" t="n">
+        <v>22606.15</v>
+      </c>
+      <c r="K40" t="n">
+        <v>-36.5</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2476,7 +2528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N39"/>
+  <dimension ref="A1:N40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4527,6 +4579,58 @@
         <v>2.04</v>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>54259.95</v>
+      </c>
+      <c r="D40" t="n">
+        <v>54259.95</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="n">
+        <v>54405.3</v>
+      </c>
+      <c r="G40" t="n">
+        <v>54514.94</v>
+      </c>
+      <c r="H40" t="n">
+        <v>-109.64</v>
+      </c>
+      <c r="I40" t="n">
+        <v>53785.7</v>
+      </c>
+      <c r="J40" t="n">
+        <v>53895.34</v>
+      </c>
+      <c r="K40" t="n">
+        <v>-109.64</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -2477,31 +2477,31 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>22716.2</v>
+        <v>22780.25</v>
       </c>
       <c r="D40" t="n">
         <v>22716.2</v>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>64.05</v>
       </c>
       <c r="F40" t="n">
-        <v>22753.25</v>
+        <v>23080.25</v>
       </c>
       <c r="G40" t="n">
         <v>22789.75</v>
       </c>
       <c r="H40" t="n">
-        <v>-36.5</v>
+        <v>290.5</v>
       </c>
       <c r="I40" t="n">
-        <v>22569.65</v>
+        <v>22762.2</v>
       </c>
       <c r="J40" t="n">
         <v>22606.15</v>
       </c>
       <c r="K40" t="n">
-        <v>-36.5</v>
+        <v>156.05</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>0.28</v>
       </c>
     </row>
   </sheetData>
@@ -4591,31 +4591,31 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>54259.95</v>
+        <v>54471.65</v>
       </c>
       <c r="D40" t="n">
         <v>54259.95</v>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>211.7</v>
       </c>
       <c r="F40" t="n">
-        <v>54405.3</v>
+        <v>55390.1</v>
       </c>
       <c r="G40" t="n">
         <v>54514.94</v>
       </c>
       <c r="H40" t="n">
-        <v>-109.64</v>
+        <v>875.16</v>
       </c>
       <c r="I40" t="n">
-        <v>53785.7</v>
+        <v>54437.7</v>
       </c>
       <c r="J40" t="n">
         <v>53895.34</v>
       </c>
       <c r="K40" t="n">
-        <v>-109.64</v>
+        <v>542.36</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>0.39</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N40"/>
+  <dimension ref="A1:N41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2515,6 +2515,58 @@
       </c>
       <c r="N40" t="n">
         <v>0.28</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>22620.45</v>
+      </c>
+      <c r="D41" t="n">
+        <v>22620.45</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>22809.35</v>
+      </c>
+      <c r="G41" t="n">
+        <v>22754.8</v>
+      </c>
+      <c r="H41" t="n">
+        <v>54.55</v>
+      </c>
+      <c r="I41" t="n">
+        <v>22595.2</v>
+      </c>
+      <c r="J41" t="n">
+        <v>22540.65</v>
+      </c>
+      <c r="K41" t="n">
+        <v>54.55</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2528,7 +2580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N40"/>
+  <dimension ref="A1:N41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4631,6 +4683,58 @@
         <v>0.39</v>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>54633.05</v>
+      </c>
+      <c r="D41" t="n">
+        <v>54633.05</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>55135.5</v>
+      </c>
+      <c r="G41" t="n">
+        <v>55120.94</v>
+      </c>
+      <c r="H41" t="n">
+        <v>14.56</v>
+      </c>
+      <c r="I41" t="n">
+        <v>54174.3</v>
+      </c>
+      <c r="J41" t="n">
+        <v>54159.74</v>
+      </c>
+      <c r="K41" t="n">
+        <v>14.56</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -2529,31 +2529,31 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>22620.45</v>
+        <v>22716.2</v>
       </c>
       <c r="D41" t="n">
         <v>22620.45</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>95.75</v>
       </c>
       <c r="F41" t="n">
-        <v>22809.35</v>
+        <v>22753.25</v>
       </c>
       <c r="G41" t="n">
         <v>22754.8</v>
       </c>
       <c r="H41" t="n">
-        <v>54.55</v>
+        <v>-1.55</v>
       </c>
       <c r="I41" t="n">
-        <v>22595.2</v>
+        <v>22569.65</v>
       </c>
       <c r="J41" t="n">
         <v>22540.65</v>
       </c>
       <c r="K41" t="n">
-        <v>54.55</v>
+        <v>29</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>0.42</v>
       </c>
     </row>
   </sheetData>
@@ -4695,31 +4695,31 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>54633.05</v>
+        <v>54259.95</v>
       </c>
       <c r="D41" t="n">
         <v>54633.05</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>-373.1</v>
       </c>
       <c r="F41" t="n">
-        <v>55135.5</v>
+        <v>54405.3</v>
       </c>
       <c r="G41" t="n">
         <v>55120.94</v>
       </c>
       <c r="H41" t="n">
-        <v>14.56</v>
+        <v>-715.64</v>
       </c>
       <c r="I41" t="n">
-        <v>54174.3</v>
+        <v>53785.7</v>
       </c>
       <c r="J41" t="n">
         <v>54159.74</v>
       </c>
       <c r="K41" t="n">
-        <v>14.56</v>
+        <v>-374.04</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>0.68</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N41"/>
+  <dimension ref="A1:N42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2567,6 +2567,58 @@
       </c>
       <c r="N41" t="n">
         <v>0.42</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>22421.95</v>
+      </c>
+      <c r="D42" t="n">
+        <v>22421.95</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="n">
+        <v>22610.6</v>
+      </c>
+      <c r="G42" t="n">
+        <v>22615.94</v>
+      </c>
+      <c r="H42" t="n">
+        <v>-5.34</v>
+      </c>
+      <c r="I42" t="n">
+        <v>22217.3</v>
+      </c>
+      <c r="J42" t="n">
+        <v>22222.64</v>
+      </c>
+      <c r="K42" t="n">
+        <v>-5.34</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2580,7 +2632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N41"/>
+  <dimension ref="A1:N42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4735,6 +4787,58 @@
         <v>0.68</v>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>54450.75</v>
+      </c>
+      <c r="D42" t="n">
+        <v>54450.75</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="n">
+        <v>55091.45</v>
+      </c>
+      <c r="G42" t="n">
+        <v>55005.94</v>
+      </c>
+      <c r="H42" t="n">
+        <v>85.51000000000001</v>
+      </c>
+      <c r="I42" t="n">
+        <v>54066.6</v>
+      </c>
+      <c r="J42" t="n">
+        <v>53981.09</v>
+      </c>
+      <c r="K42" t="n">
+        <v>85.51000000000001</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -2581,31 +2581,31 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>22421.95</v>
+        <v>22620.45</v>
       </c>
       <c r="D42" t="n">
         <v>22421.95</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>198.5</v>
       </c>
       <c r="F42" t="n">
-        <v>22610.6</v>
+        <v>22809.35</v>
       </c>
       <c r="G42" t="n">
         <v>22615.94</v>
       </c>
       <c r="H42" t="n">
-        <v>-5.34</v>
+        <v>193.41</v>
       </c>
       <c r="I42" t="n">
-        <v>22217.3</v>
+        <v>22595.2</v>
       </c>
       <c r="J42" t="n">
         <v>22222.64</v>
       </c>
       <c r="K42" t="n">
-        <v>-5.34</v>
+        <v>372.56</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>0.89</v>
       </c>
     </row>
   </sheetData>
@@ -4799,31 +4799,31 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>54450.75</v>
+        <v>54633.05</v>
       </c>
       <c r="D42" t="n">
         <v>54450.75</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>182.3</v>
       </c>
       <c r="F42" t="n">
-        <v>55091.45</v>
+        <v>55135.5</v>
       </c>
       <c r="G42" t="n">
         <v>55005.94</v>
       </c>
       <c r="H42" t="n">
-        <v>85.51000000000001</v>
+        <v>129.56</v>
       </c>
       <c r="I42" t="n">
-        <v>54066.6</v>
+        <v>54174.3</v>
       </c>
       <c r="J42" t="n">
         <v>53981.09</v>
       </c>
       <c r="K42" t="n">
-        <v>85.51000000000001</v>
+        <v>193.21</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -4836,7 +4836,7 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -2581,31 +2581,31 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>22620.45</v>
+        <v>22421.95</v>
       </c>
       <c r="D42" t="n">
         <v>22421.95</v>
       </c>
       <c r="E42" t="n">
-        <v>198.5</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>22809.35</v>
+        <v>22610.6</v>
       </c>
       <c r="G42" t="n">
         <v>22615.94</v>
       </c>
       <c r="H42" t="n">
-        <v>193.41</v>
+        <v>-5.34</v>
       </c>
       <c r="I42" t="n">
-        <v>22595.2</v>
+        <v>22217.3</v>
       </c>
       <c r="J42" t="n">
         <v>22222.64</v>
       </c>
       <c r="K42" t="n">
-        <v>372.56</v>
+        <v>-5.34</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>0.89</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4799,31 +4799,31 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>54633.05</v>
+        <v>54450.75</v>
       </c>
       <c r="D42" t="n">
         <v>54450.75</v>
       </c>
       <c r="E42" t="n">
-        <v>182.3</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>55135.5</v>
+        <v>55091.45</v>
       </c>
       <c r="G42" t="n">
         <v>55005.94</v>
       </c>
       <c r="H42" t="n">
-        <v>129.56</v>
+        <v>85.51000000000001</v>
       </c>
       <c r="I42" t="n">
-        <v>54174.3</v>
+        <v>54066.6</v>
       </c>
       <c r="J42" t="n">
         <v>53981.09</v>
       </c>
       <c r="K42" t="n">
-        <v>193.21</v>
+        <v>85.51000000000001</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -4836,7 +4836,7 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N42"/>
+  <dimension ref="A1:N43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2619,6 +2619,58 @@
       </c>
       <c r="N42" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>22421.95</v>
+      </c>
+      <c r="D43" t="n">
+        <v>22439.25</v>
+      </c>
+      <c r="E43" t="n">
+        <v>-17.3</v>
+      </c>
+      <c r="F43" t="n">
+        <v>22610.6</v>
+      </c>
+      <c r="G43" t="n">
+        <v>22575</v>
+      </c>
+      <c r="H43" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="I43" t="n">
+        <v>22217.3</v>
+      </c>
+      <c r="J43" t="n">
+        <v>22350.3</v>
+      </c>
+      <c r="K43" t="n">
+        <v>-133</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N43" t="n">
+        <v>0.08</v>
       </c>
     </row>
   </sheetData>
@@ -2632,7 +2684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N42"/>
+  <dimension ref="A1:N43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4839,6 +4891,58 @@
         <v>0</v>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>54450.75</v>
+      </c>
+      <c r="D43" t="n">
+        <v>54583.35</v>
+      </c>
+      <c r="E43" t="n">
+        <v>-132.6</v>
+      </c>
+      <c r="F43" t="n">
+        <v>55091.45</v>
+      </c>
+      <c r="G43" t="n">
+        <v>55060.46</v>
+      </c>
+      <c r="H43" t="n">
+        <v>30.99</v>
+      </c>
+      <c r="I43" t="n">
+        <v>54066.6</v>
+      </c>
+      <c r="J43" t="n">
+        <v>54238.41</v>
+      </c>
+      <c r="K43" t="n">
+        <v>-171.81</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N43" t="n">
+        <v>0.24</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N43"/>
+  <dimension ref="A1:N44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2671,6 +2671,58 @@
       </c>
       <c r="N43" t="n">
         <v>0.08</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>22776.1</v>
+      </c>
+      <c r="D44" t="n">
+        <v>22776.1</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>22776.1</v>
+      </c>
+      <c r="G44" t="n">
+        <v>22847.6</v>
+      </c>
+      <c r="H44" t="n">
+        <v>-71.5</v>
+      </c>
+      <c r="I44" t="n">
+        <v>22561.6</v>
+      </c>
+      <c r="J44" t="n">
+        <v>22633.1</v>
+      </c>
+      <c r="K44" t="n">
+        <v>-71.5</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N44" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2684,7 +2736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N43"/>
+  <dimension ref="A1:N44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4943,6 +4995,58 @@
         <v>0.24</v>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>55128.4</v>
+      </c>
+      <c r="D44" t="n">
+        <v>55128.4</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>55201</v>
+      </c>
+      <c r="G44" t="n">
+        <v>55274.69</v>
+      </c>
+      <c r="H44" t="n">
+        <v>-73.69</v>
+      </c>
+      <c r="I44" t="n">
+        <v>54834.75</v>
+      </c>
+      <c r="J44" t="n">
+        <v>54908.44</v>
+      </c>
+      <c r="K44" t="n">
+        <v>-73.69</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -2685,31 +2685,31 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>22776.1</v>
+        <v>22555.75</v>
       </c>
       <c r="D44" t="n">
         <v>22776.1</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>-220.35</v>
       </c>
       <c r="F44" t="n">
-        <v>22776.1</v>
+        <v>22621.8</v>
       </c>
       <c r="G44" t="n">
         <v>22847.6</v>
       </c>
       <c r="H44" t="n">
-        <v>-71.5</v>
+        <v>-225.8</v>
       </c>
       <c r="I44" t="n">
-        <v>22561.6</v>
+        <v>22397.1</v>
       </c>
       <c r="J44" t="n">
         <v>22633.1</v>
       </c>
       <c r="K44" t="n">
-        <v>-71.5</v>
+        <v>-236</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>0.97</v>
       </c>
     </row>
   </sheetData>
@@ -5007,31 +5007,31 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>55128.4</v>
+        <v>54714.1</v>
       </c>
       <c r="D44" t="n">
         <v>55128.4</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>-414.3</v>
       </c>
       <c r="F44" t="n">
-        <v>55201</v>
+        <v>55192.65</v>
       </c>
       <c r="G44" t="n">
         <v>55274.69</v>
       </c>
       <c r="H44" t="n">
-        <v>-73.69</v>
+        <v>-82.04000000000001</v>
       </c>
       <c r="I44" t="n">
-        <v>54834.75</v>
+        <v>54370.6</v>
       </c>
       <c r="J44" t="n">
         <v>54908.44</v>
       </c>
       <c r="K44" t="n">
-        <v>-73.69</v>
+        <v>-537.84</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -5044,7 +5044,7 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N44"/>
+  <dimension ref="A1:N45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2723,6 +2723,58 @@
       </c>
       <c r="N44" t="n">
         <v>0.97</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>22603.05</v>
+      </c>
+      <c r="D45" t="n">
+        <v>22603.05</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="n">
+        <v>22717.65</v>
+      </c>
+      <c r="G45" t="n">
+        <v>22698.36</v>
+      </c>
+      <c r="H45" t="n">
+        <v>19.29</v>
+      </c>
+      <c r="I45" t="n">
+        <v>22546.3</v>
+      </c>
+      <c r="J45" t="n">
+        <v>22527.01</v>
+      </c>
+      <c r="K45" t="n">
+        <v>19.29</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2736,7 +2788,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N44"/>
+  <dimension ref="A1:N45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5047,6 +5099,58 @@
         <v>0.75</v>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>55055.55</v>
+      </c>
+      <c r="D45" t="n">
+        <v>55055.55</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="n">
+        <v>55340.7</v>
+      </c>
+      <c r="G45" t="n">
+        <v>55385.44</v>
+      </c>
+      <c r="H45" t="n">
+        <v>-44.74</v>
+      </c>
+      <c r="I45" t="n">
+        <v>54636.2</v>
+      </c>
+      <c r="J45" t="n">
+        <v>54680.94</v>
+      </c>
+      <c r="K45" t="n">
+        <v>-44.74</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -2737,31 +2737,31 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>22603.05</v>
+        <v>22776.1</v>
       </c>
       <c r="D45" t="n">
         <v>22603.05</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>173.05</v>
       </c>
       <c r="F45" t="n">
-        <v>22717.65</v>
+        <v>22776.1</v>
       </c>
       <c r="G45" t="n">
         <v>22698.36</v>
       </c>
       <c r="H45" t="n">
-        <v>19.29</v>
+        <v>77.73999999999999</v>
       </c>
       <c r="I45" t="n">
-        <v>22546.3</v>
+        <v>22561.6</v>
       </c>
       <c r="J45" t="n">
         <v>22527.01</v>
       </c>
       <c r="K45" t="n">
-        <v>19.29</v>
+        <v>34.59</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>0.77</v>
       </c>
     </row>
   </sheetData>
@@ -5111,31 +5111,31 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>55055.55</v>
+        <v>55128.4</v>
       </c>
       <c r="D45" t="n">
         <v>55055.55</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>72.84999999999999</v>
       </c>
       <c r="F45" t="n">
-        <v>55340.7</v>
+        <v>55201</v>
       </c>
       <c r="G45" t="n">
         <v>55385.44</v>
       </c>
       <c r="H45" t="n">
-        <v>-44.74</v>
+        <v>-184.44</v>
       </c>
       <c r="I45" t="n">
-        <v>54636.2</v>
+        <v>54834.75</v>
       </c>
       <c r="J45" t="n">
         <v>54680.94</v>
       </c>
       <c r="K45" t="n">
-        <v>-44.74</v>
+        <v>153.81</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -5148,7 +5148,7 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>0.13</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N45"/>
+  <dimension ref="A1:N46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2775,6 +2775,58 @@
       </c>
       <c r="N45" t="n">
         <v>0.77</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>22231.8</v>
+      </c>
+      <c r="D46" t="n">
+        <v>22231.8</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="n">
+        <v>22599.05</v>
+      </c>
+      <c r="G46" t="n">
+        <v>22493.94</v>
+      </c>
+      <c r="H46" t="n">
+        <v>105.11</v>
+      </c>
+      <c r="I46" t="n">
+        <v>22179.9</v>
+      </c>
+      <c r="J46" t="n">
+        <v>22074.79</v>
+      </c>
+      <c r="K46" t="n">
+        <v>105.11</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2788,7 +2840,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N45"/>
+  <dimension ref="A1:N46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5151,6 +5203,58 @@
         <v>0.13</v>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>54515.05</v>
+      </c>
+      <c r="D46" t="n">
+        <v>54515.05</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="n">
+        <v>55043</v>
+      </c>
+      <c r="G46" t="n">
+        <v>54910.99</v>
+      </c>
+      <c r="H46" t="n">
+        <v>132.01</v>
+      </c>
+      <c r="I46" t="n">
+        <v>54383.15</v>
+      </c>
+      <c r="J46" t="n">
+        <v>54251.14</v>
+      </c>
+      <c r="K46" t="n">
+        <v>132.01</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -2789,31 +2789,31 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>22231.8</v>
+        <v>22603.05</v>
       </c>
       <c r="D46" t="n">
         <v>22231.8</v>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
+        <v>371.25</v>
       </c>
       <c r="F46" t="n">
-        <v>22599.05</v>
+        <v>22717.65</v>
       </c>
       <c r="G46" t="n">
         <v>22493.94</v>
       </c>
       <c r="H46" t="n">
-        <v>105.11</v>
+        <v>223.71</v>
       </c>
       <c r="I46" t="n">
-        <v>22179.9</v>
+        <v>22546.3</v>
       </c>
       <c r="J46" t="n">
         <v>22074.79</v>
       </c>
       <c r="K46" t="n">
-        <v>105.11</v>
+        <v>471.51</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
     </row>
   </sheetData>
@@ -5215,31 +5215,31 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>54515.05</v>
+        <v>55055.55</v>
       </c>
       <c r="D46" t="n">
         <v>54515.05</v>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
+        <v>540.5</v>
       </c>
       <c r="F46" t="n">
-        <v>55043</v>
+        <v>55340.7</v>
       </c>
       <c r="G46" t="n">
         <v>54910.99</v>
       </c>
       <c r="H46" t="n">
-        <v>132.01</v>
+        <v>429.71</v>
       </c>
       <c r="I46" t="n">
-        <v>54383.15</v>
+        <v>54636.2</v>
       </c>
       <c r="J46" t="n">
         <v>54251.14</v>
       </c>
       <c r="K46" t="n">
-        <v>132.01</v>
+        <v>385.06</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>0.99</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N46"/>
+  <dimension ref="A1:N47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2827,6 +2827,58 @@
       </c>
       <c r="N46" t="n">
         <v>1.67</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>22520.45</v>
+      </c>
+      <c r="D47" t="n">
+        <v>22520.45</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" t="n">
+        <v>22580.75</v>
+      </c>
+      <c r="G47" t="n">
+        <v>22635.89</v>
+      </c>
+      <c r="H47" t="n">
+        <v>-55.14</v>
+      </c>
+      <c r="I47" t="n">
+        <v>22294.75</v>
+      </c>
+      <c r="J47" t="n">
+        <v>22349.89</v>
+      </c>
+      <c r="K47" t="n">
+        <v>-55.14</v>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2840,7 +2892,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N46"/>
+  <dimension ref="A1:N47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5255,6 +5307,58 @@
         <v>0.99</v>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>55256.65</v>
+      </c>
+      <c r="D47" t="n">
+        <v>55256.65</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" t="n">
+        <v>55419.3</v>
+      </c>
+      <c r="G47" t="n">
+        <v>55578.24</v>
+      </c>
+      <c r="H47" t="n">
+        <v>-158.94</v>
+      </c>
+      <c r="I47" t="n">
+        <v>54617.2</v>
+      </c>
+      <c r="J47" t="n">
+        <v>54776.14</v>
+      </c>
+      <c r="K47" t="n">
+        <v>-158.94</v>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -2841,31 +2841,31 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>22520.45</v>
+        <v>22231.8</v>
       </c>
       <c r="D47" t="n">
         <v>22520.45</v>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>-288.65</v>
       </c>
       <c r="F47" t="n">
-        <v>22580.75</v>
+        <v>22599.05</v>
       </c>
       <c r="G47" t="n">
         <v>22635.89</v>
       </c>
       <c r="H47" t="n">
-        <v>-55.14</v>
+        <v>-36.84</v>
       </c>
       <c r="I47" t="n">
-        <v>22294.75</v>
+        <v>22179.9</v>
       </c>
       <c r="J47" t="n">
         <v>22349.89</v>
       </c>
       <c r="K47" t="n">
-        <v>-55.14</v>
+        <v>-169.99</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
     </row>
   </sheetData>
@@ -5319,31 +5319,31 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>55256.65</v>
+        <v>54515.05</v>
       </c>
       <c r="D47" t="n">
         <v>55256.65</v>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>-741.6</v>
       </c>
       <c r="F47" t="n">
-        <v>55419.3</v>
+        <v>55043</v>
       </c>
       <c r="G47" t="n">
         <v>55578.24</v>
       </c>
       <c r="H47" t="n">
-        <v>-158.94</v>
+        <v>-535.24</v>
       </c>
       <c r="I47" t="n">
-        <v>54617.2</v>
+        <v>54383.15</v>
       </c>
       <c r="J47" t="n">
         <v>54776.14</v>
       </c>
       <c r="K47" t="n">
-        <v>-158.94</v>
+        <v>-392.99</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -5356,7 +5356,7 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -2841,31 +2841,31 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>22231.8</v>
+        <v>22520.45</v>
       </c>
       <c r="D47" t="n">
         <v>22520.45</v>
       </c>
       <c r="E47" t="n">
-        <v>-288.65</v>
+        <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>22599.05</v>
+        <v>22580.75</v>
       </c>
       <c r="G47" t="n">
         <v>22635.89</v>
       </c>
       <c r="H47" t="n">
-        <v>-36.84</v>
+        <v>-55.14</v>
       </c>
       <c r="I47" t="n">
-        <v>22179.9</v>
+        <v>22294.75</v>
       </c>
       <c r="J47" t="n">
         <v>22349.89</v>
       </c>
       <c r="K47" t="n">
-        <v>-169.99</v>
+        <v>-55.14</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -5319,31 +5319,31 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>54515.05</v>
+        <v>55256.65</v>
       </c>
       <c r="D47" t="n">
         <v>55256.65</v>
       </c>
       <c r="E47" t="n">
-        <v>-741.6</v>
+        <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>55043</v>
+        <v>55419.3</v>
       </c>
       <c r="G47" t="n">
         <v>55578.24</v>
       </c>
       <c r="H47" t="n">
-        <v>-535.24</v>
+        <v>-158.94</v>
       </c>
       <c r="I47" t="n">
-        <v>54383.15</v>
+        <v>54617.2</v>
       </c>
       <c r="J47" t="n">
         <v>54776.14</v>
       </c>
       <c r="K47" t="n">
-        <v>-392.99</v>
+        <v>-158.94</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -5356,7 +5356,7 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N47"/>
+  <dimension ref="A1:N48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2879,6 +2879,58 @@
       </c>
       <c r="N47" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>22520.45</v>
+      </c>
+      <c r="D48" t="n">
+        <v>22400</v>
+      </c>
+      <c r="E48" t="n">
+        <v>120.45</v>
+      </c>
+      <c r="F48" t="n">
+        <v>22580.75</v>
+      </c>
+      <c r="G48" t="n">
+        <v>22583.29</v>
+      </c>
+      <c r="H48" t="n">
+        <v>-2.54</v>
+      </c>
+      <c r="I48" t="n">
+        <v>22294.75</v>
+      </c>
+      <c r="J48" t="n">
+        <v>22284.54</v>
+      </c>
+      <c r="K48" t="n">
+        <v>10.21</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N48" t="n">
+        <v>0.54</v>
       </c>
     </row>
   </sheetData>
@@ -2892,7 +2944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N47"/>
+  <dimension ref="A1:N48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5359,6 +5411,58 @@
         <v>0</v>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>55256.65</v>
+      </c>
+      <c r="D48" t="n">
+        <v>54904.05</v>
+      </c>
+      <c r="E48" t="n">
+        <v>352.6</v>
+      </c>
+      <c r="F48" t="n">
+        <v>55419.3</v>
+      </c>
+      <c r="G48" t="n">
+        <v>55310.65</v>
+      </c>
+      <c r="H48" t="n">
+        <v>108.65</v>
+      </c>
+      <c r="I48" t="n">
+        <v>54617.2</v>
+      </c>
+      <c r="J48" t="n">
+        <v>54603.25</v>
+      </c>
+      <c r="K48" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N48" t="n">
+        <v>0.64</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -2893,31 +2893,31 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>22520.45</v>
+        <v>22363.35</v>
       </c>
       <c r="D48" t="n">
         <v>22400</v>
       </c>
       <c r="E48" t="n">
-        <v>120.45</v>
+        <v>-36.65</v>
       </c>
       <c r="F48" t="n">
-        <v>22580.75</v>
+        <v>22651.1</v>
       </c>
       <c r="G48" t="n">
         <v>22583.29</v>
       </c>
       <c r="H48" t="n">
-        <v>-2.54</v>
+        <v>67.81</v>
       </c>
       <c r="I48" t="n">
-        <v>22294.75</v>
+        <v>22304.45</v>
       </c>
       <c r="J48" t="n">
         <v>22284.54</v>
       </c>
       <c r="K48" t="n">
-        <v>10.21</v>
+        <v>19.91</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>0.54</v>
+        <v>0.16</v>
       </c>
     </row>
   </sheetData>
@@ -5423,31 +5423,31 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>55256.65</v>
+        <v>54918</v>
       </c>
       <c r="D48" t="n">
         <v>54904.05</v>
       </c>
       <c r="E48" t="n">
-        <v>352.6</v>
+        <v>13.95</v>
       </c>
       <c r="F48" t="n">
-        <v>55419.3</v>
+        <v>55416.45</v>
       </c>
       <c r="G48" t="n">
         <v>55310.65</v>
       </c>
       <c r="H48" t="n">
-        <v>108.65</v>
+        <v>105.8</v>
       </c>
       <c r="I48" t="n">
-        <v>54617.2</v>
+        <v>54708.8</v>
       </c>
       <c r="J48" t="n">
         <v>54603.25</v>
       </c>
       <c r="K48" t="n">
-        <v>13.95</v>
+        <v>105.55</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>0.64</v>
+        <v>0.03</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N48"/>
+  <dimension ref="A1:N49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2931,6 +2931,58 @@
       </c>
       <c r="N48" t="n">
         <v>0.16</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>22721.95</v>
+      </c>
+      <c r="D49" t="n">
+        <v>22721.95</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" t="n">
+        <v>22721.95</v>
+      </c>
+      <c r="G49" t="n">
+        <v>22866.45</v>
+      </c>
+      <c r="H49" t="n">
+        <v>-144.5</v>
+      </c>
+      <c r="I49" t="n">
+        <v>22288.45</v>
+      </c>
+      <c r="J49" t="n">
+        <v>22432.95</v>
+      </c>
+      <c r="K49" t="n">
+        <v>-144.5</v>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N49" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2944,7 +2996,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N48"/>
+  <dimension ref="A1:N49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5463,6 +5515,58 @@
         <v>0.03</v>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>55481.05</v>
+      </c>
+      <c r="D49" t="n">
+        <v>55481.05</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" t="n">
+        <v>55551.75</v>
+      </c>
+      <c r="G49" t="n">
+        <v>55776.55</v>
+      </c>
+      <c r="H49" t="n">
+        <v>-224.8</v>
+      </c>
+      <c r="I49" t="n">
+        <v>54735.95</v>
+      </c>
+      <c r="J49" t="n">
+        <v>54960.75</v>
+      </c>
+      <c r="K49" t="n">
+        <v>-224.8</v>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N49" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -2945,31 +2945,31 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>22721.95</v>
+        <v>22363.35</v>
       </c>
       <c r="D49" t="n">
         <v>22721.95</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>-358.6</v>
       </c>
       <c r="F49" t="n">
-        <v>22721.95</v>
+        <v>22651.1</v>
       </c>
       <c r="G49" t="n">
         <v>22866.45</v>
       </c>
       <c r="H49" t="n">
-        <v>-144.5</v>
+        <v>-215.35</v>
       </c>
       <c r="I49" t="n">
-        <v>22288.45</v>
+        <v>22304.45</v>
       </c>
       <c r="J49" t="n">
         <v>22432.95</v>
       </c>
       <c r="K49" t="n">
-        <v>-144.5</v>
+        <v>-128.5</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
     </row>
   </sheetData>
@@ -5527,31 +5527,31 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>55481.05</v>
+        <v>54918</v>
       </c>
       <c r="D49" t="n">
         <v>55481.05</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>-563.05</v>
       </c>
       <c r="F49" t="n">
-        <v>55551.75</v>
+        <v>55416.45</v>
       </c>
       <c r="G49" t="n">
         <v>55776.55</v>
       </c>
       <c r="H49" t="n">
-        <v>-224.8</v>
+        <v>-360.1</v>
       </c>
       <c r="I49" t="n">
-        <v>54735.95</v>
+        <v>54708.8</v>
       </c>
       <c r="J49" t="n">
         <v>54960.75</v>
       </c>
       <c r="K49" t="n">
-        <v>-224.8</v>
+        <v>-251.95</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -5564,7 +5564,7 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N49"/>
+  <dimension ref="A1:N50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2983,6 +2983,58 @@
       </c>
       <c r="N49" t="n">
         <v>1.58</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>22622.7</v>
+      </c>
+      <c r="D50" t="n">
+        <v>22622.7</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" t="n">
+        <v>22757.95</v>
+      </c>
+      <c r="G50" t="n">
+        <v>22734.11</v>
+      </c>
+      <c r="H50" t="n">
+        <v>23.84</v>
+      </c>
+      <c r="I50" t="n">
+        <v>22558.95</v>
+      </c>
+      <c r="J50" t="n">
+        <v>22535.11</v>
+      </c>
+      <c r="K50" t="n">
+        <v>23.84</v>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N50" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2996,7 +3048,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N49"/>
+  <dimension ref="A1:N50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5567,6 +5619,58 @@
         <v>1.01</v>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>55316</v>
+      </c>
+      <c r="D50" t="n">
+        <v>55316</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" t="n">
+        <v>55644.7</v>
+      </c>
+      <c r="G50" t="n">
+        <v>55584.4</v>
+      </c>
+      <c r="H50" t="n">
+        <v>60.3</v>
+      </c>
+      <c r="I50" t="n">
+        <v>55168.2</v>
+      </c>
+      <c r="J50" t="n">
+        <v>55107.9</v>
+      </c>
+      <c r="K50" t="n">
+        <v>60.3</v>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N50" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -2997,31 +2997,31 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>22622.7</v>
+        <v>22721.95</v>
       </c>
       <c r="D50" t="n">
         <v>22622.7</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>99.25</v>
       </c>
       <c r="F50" t="n">
-        <v>22757.95</v>
+        <v>22721.95</v>
       </c>
       <c r="G50" t="n">
         <v>22734.11</v>
       </c>
       <c r="H50" t="n">
-        <v>23.84</v>
+        <v>-12.16</v>
       </c>
       <c r="I50" t="n">
-        <v>22558.95</v>
+        <v>22288.45</v>
       </c>
       <c r="J50" t="n">
         <v>22535.11</v>
       </c>
       <c r="K50" t="n">
-        <v>23.84</v>
+        <v>-246.66</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>0.44</v>
       </c>
     </row>
   </sheetData>
@@ -5631,31 +5631,31 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>55316</v>
+        <v>55481.05</v>
       </c>
       <c r="D50" t="n">
         <v>55316</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>165.05</v>
       </c>
       <c r="F50" t="n">
-        <v>55644.7</v>
+        <v>55551.75</v>
       </c>
       <c r="G50" t="n">
         <v>55584.4</v>
       </c>
       <c r="H50" t="n">
-        <v>60.3</v>
+        <v>-32.65</v>
       </c>
       <c r="I50" t="n">
-        <v>55168.2</v>
+        <v>54735.95</v>
       </c>
       <c r="J50" t="n">
         <v>55107.9</v>
       </c>
       <c r="K50" t="n">
-        <v>60.3</v>
+        <v>-371.95</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N50"/>
+  <dimension ref="A1:N51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3035,6 +3035,58 @@
       </c>
       <c r="N50" t="n">
         <v>0.44</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>22997.35</v>
+      </c>
+      <c r="D51" t="n">
+        <v>22997.35</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" t="n">
+        <v>23056.4</v>
+      </c>
+      <c r="G51" t="n">
+        <v>23156.7</v>
+      </c>
+      <c r="H51" t="n">
+        <v>-100.3</v>
+      </c>
+      <c r="I51" t="n">
+        <v>22637.4</v>
+      </c>
+      <c r="J51" t="n">
+        <v>22737.7</v>
+      </c>
+      <c r="K51" t="n">
+        <v>-100.3</v>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N51" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3048,7 +3100,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N50"/>
+  <dimension ref="A1:N51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5671,6 +5723,58 @@
         <v>0.3</v>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>55810.5</v>
+      </c>
+      <c r="D51" t="n">
+        <v>55810.5</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" t="n">
+        <v>56065.5</v>
+      </c>
+      <c r="G51" t="n">
+        <v>56157.66</v>
+      </c>
+      <c r="H51" t="n">
+        <v>-92.16</v>
+      </c>
+      <c r="I51" t="n">
+        <v>55279</v>
+      </c>
+      <c r="J51" t="n">
+        <v>55371.16</v>
+      </c>
+      <c r="K51" t="n">
+        <v>-92.16</v>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N51" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -3049,31 +3049,31 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>22997.35</v>
+        <v>22622.7</v>
       </c>
       <c r="D51" t="n">
         <v>22997.35</v>
       </c>
       <c r="E51" t="n">
-        <v>0</v>
+        <v>-374.65</v>
       </c>
       <c r="F51" t="n">
-        <v>23056.4</v>
+        <v>22757.95</v>
       </c>
       <c r="G51" t="n">
         <v>23156.7</v>
       </c>
       <c r="H51" t="n">
-        <v>-100.3</v>
+        <v>-398.75</v>
       </c>
       <c r="I51" t="n">
-        <v>22637.4</v>
+        <v>22558.95</v>
       </c>
       <c r="J51" t="n">
         <v>22737.7</v>
       </c>
       <c r="K51" t="n">
-        <v>-100.3</v>
+        <v>-178.75</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
     </row>
   </sheetData>
@@ -5735,31 +5735,31 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>55810.5</v>
+        <v>55316</v>
       </c>
       <c r="D51" t="n">
         <v>55810.5</v>
       </c>
       <c r="E51" t="n">
-        <v>0</v>
+        <v>-494.5</v>
       </c>
       <c r="F51" t="n">
-        <v>56065.5</v>
+        <v>55644.7</v>
       </c>
       <c r="G51" t="n">
         <v>56157.66</v>
       </c>
       <c r="H51" t="n">
-        <v>-92.16</v>
+        <v>-512.96</v>
       </c>
       <c r="I51" t="n">
-        <v>55279</v>
+        <v>55168.2</v>
       </c>
       <c r="J51" t="n">
         <v>55371.16</v>
       </c>
       <c r="K51" t="n">
-        <v>-92.16</v>
+        <v>-202.96</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -5772,7 +5772,7 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>0.89</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N51"/>
+  <dimension ref="A1:N52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3087,6 +3087,58 @@
       </c>
       <c r="N51" t="n">
         <v>1.63</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>23146.15</v>
+      </c>
+      <c r="D52" t="n">
+        <v>23146.15</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" t="n">
+        <v>23149.85</v>
+      </c>
+      <c r="G52" t="n">
+        <v>23226.06</v>
+      </c>
+      <c r="H52" t="n">
+        <v>-76.20999999999999</v>
+      </c>
+      <c r="I52" t="n">
+        <v>22913.8</v>
+      </c>
+      <c r="J52" t="n">
+        <v>22990.01</v>
+      </c>
+      <c r="K52" t="n">
+        <v>-76.20999999999999</v>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N52" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3100,7 +3152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N51"/>
+  <dimension ref="A1:N52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5775,6 +5827,58 @@
         <v>0.89</v>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>55844</v>
+      </c>
+      <c r="D52" t="n">
+        <v>55844</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" t="n">
+        <v>55989.55</v>
+      </c>
+      <c r="G52" t="n">
+        <v>56046.94</v>
+      </c>
+      <c r="H52" t="n">
+        <v>-57.39</v>
+      </c>
+      <c r="I52" t="n">
+        <v>55526.3</v>
+      </c>
+      <c r="J52" t="n">
+        <v>55583.69</v>
+      </c>
+      <c r="K52" t="n">
+        <v>-57.39</v>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N52" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -3101,31 +3101,31 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>23146.15</v>
+        <v>22997.35</v>
       </c>
       <c r="D52" t="n">
         <v>23146.15</v>
       </c>
       <c r="E52" t="n">
-        <v>0</v>
+        <v>-148.8</v>
       </c>
       <c r="F52" t="n">
-        <v>23149.85</v>
+        <v>23056.4</v>
       </c>
       <c r="G52" t="n">
         <v>23226.06</v>
       </c>
       <c r="H52" t="n">
-        <v>-76.20999999999999</v>
+        <v>-169.66</v>
       </c>
       <c r="I52" t="n">
-        <v>22913.8</v>
+        <v>22637.4</v>
       </c>
       <c r="J52" t="n">
         <v>22990.01</v>
       </c>
       <c r="K52" t="n">
-        <v>-76.20999999999999</v>
+        <v>-352.61</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>0.64</v>
       </c>
     </row>
   </sheetData>
@@ -5839,31 +5839,31 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>55844</v>
+        <v>55810.5</v>
       </c>
       <c r="D52" t="n">
         <v>55844</v>
       </c>
       <c r="E52" t="n">
-        <v>0</v>
+        <v>-33.5</v>
       </c>
       <c r="F52" t="n">
-        <v>55989.55</v>
+        <v>56065.5</v>
       </c>
       <c r="G52" t="n">
         <v>56046.94</v>
       </c>
       <c r="H52" t="n">
-        <v>-57.39</v>
+        <v>18.56</v>
       </c>
       <c r="I52" t="n">
-        <v>55526.3</v>
+        <v>55279</v>
       </c>
       <c r="J52" t="n">
         <v>55583.69</v>
       </c>
       <c r="K52" t="n">
-        <v>-57.39</v>
+        <v>-304.69</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -3101,31 +3101,31 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>22997.35</v>
+        <v>23146.15</v>
       </c>
       <c r="D52" t="n">
         <v>23146.15</v>
       </c>
       <c r="E52" t="n">
-        <v>-148.8</v>
+        <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>23056.4</v>
+        <v>23149.85</v>
       </c>
       <c r="G52" t="n">
         <v>23226.06</v>
       </c>
       <c r="H52" t="n">
-        <v>-169.66</v>
+        <v>-76.20999999999999</v>
       </c>
       <c r="I52" t="n">
-        <v>22637.4</v>
+        <v>22913.8</v>
       </c>
       <c r="J52" t="n">
         <v>22990.01</v>
       </c>
       <c r="K52" t="n">
-        <v>-352.61</v>
+        <v>-76.20999999999999</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>0.64</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -5839,31 +5839,31 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>55810.5</v>
+        <v>55844</v>
       </c>
       <c r="D52" t="n">
         <v>55844</v>
       </c>
       <c r="E52" t="n">
-        <v>-33.5</v>
+        <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>56065.5</v>
+        <v>55989.55</v>
       </c>
       <c r="G52" t="n">
         <v>56046.94</v>
       </c>
       <c r="H52" t="n">
-        <v>18.56</v>
+        <v>-57.39</v>
       </c>
       <c r="I52" t="n">
-        <v>55279</v>
+        <v>55526.3</v>
       </c>
       <c r="J52" t="n">
         <v>55583.69</v>
       </c>
       <c r="K52" t="n">
-        <v>-304.69</v>
+        <v>-57.39</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N52"/>
+  <dimension ref="A1:N53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3138,6 +3138,58 @@
         </is>
       </c>
       <c r="N52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>22888.95</v>
+      </c>
+      <c r="D53" t="n">
+        <v>22888.95</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" t="n">
+        <v>23175.25</v>
+      </c>
+      <c r="G53" t="n">
+        <v>23094.46</v>
+      </c>
+      <c r="H53" t="n">
+        <v>80.79000000000001</v>
+      </c>
+      <c r="I53" t="n">
+        <v>22845</v>
+      </c>
+      <c r="J53" t="n">
+        <v>22764.21</v>
+      </c>
+      <c r="K53" t="n">
+        <v>80.79000000000001</v>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N53" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3152,7 +3204,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N52"/>
+  <dimension ref="A1:N53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5879,6 +5931,58 @@
         <v>0</v>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>55488.1</v>
+      </c>
+      <c r="D53" t="n">
+        <v>55488.1</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" t="n">
+        <v>55883.7</v>
+      </c>
+      <c r="G53" t="n">
+        <v>55804.16</v>
+      </c>
+      <c r="H53" t="n">
+        <v>79.54000000000001</v>
+      </c>
+      <c r="I53" t="n">
+        <v>55331.1</v>
+      </c>
+      <c r="J53" t="n">
+        <v>55251.56</v>
+      </c>
+      <c r="K53" t="n">
+        <v>79.54000000000001</v>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N53" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -3153,31 +3153,31 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>22888.95</v>
+        <v>23146.15</v>
       </c>
       <c r="D53" t="n">
         <v>22888.95</v>
       </c>
       <c r="E53" t="n">
-        <v>0</v>
+        <v>257.2</v>
       </c>
       <c r="F53" t="n">
-        <v>23175.25</v>
+        <v>23149.85</v>
       </c>
       <c r="G53" t="n">
         <v>23094.46</v>
       </c>
       <c r="H53" t="n">
-        <v>80.79000000000001</v>
+        <v>55.39</v>
       </c>
       <c r="I53" t="n">
-        <v>22845</v>
+        <v>22913.8</v>
       </c>
       <c r="J53" t="n">
         <v>22764.21</v>
       </c>
       <c r="K53" t="n">
-        <v>80.79000000000001</v>
+        <v>149.59</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
     </row>
   </sheetData>
@@ -5943,31 +5943,31 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>55488.1</v>
+        <v>55844</v>
       </c>
       <c r="D53" t="n">
         <v>55488.1</v>
       </c>
       <c r="E53" t="n">
-        <v>0</v>
+        <v>355.9</v>
       </c>
       <c r="F53" t="n">
-        <v>55883.7</v>
+        <v>55989.55</v>
       </c>
       <c r="G53" t="n">
         <v>55804.16</v>
       </c>
       <c r="H53" t="n">
-        <v>79.54000000000001</v>
+        <v>185.39</v>
       </c>
       <c r="I53" t="n">
-        <v>55331.1</v>
+        <v>55526.3</v>
       </c>
       <c r="J53" t="n">
         <v>55251.56</v>
       </c>
       <c r="K53" t="n">
-        <v>79.54000000000001</v>
+        <v>274.74</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
@@ -5980,7 +5980,7 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>0.64</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -3153,31 +3153,31 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>23146.15</v>
+        <v>22888.95</v>
       </c>
       <c r="D53" t="n">
         <v>22888.95</v>
       </c>
       <c r="E53" t="n">
-        <v>257.2</v>
+        <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>23149.85</v>
+        <v>23175.25</v>
       </c>
       <c r="G53" t="n">
         <v>23094.46</v>
       </c>
       <c r="H53" t="n">
-        <v>55.39</v>
+        <v>80.79000000000001</v>
       </c>
       <c r="I53" t="n">
-        <v>22913.8</v>
+        <v>22845</v>
       </c>
       <c r="J53" t="n">
         <v>22764.21</v>
       </c>
       <c r="K53" t="n">
-        <v>149.59</v>
+        <v>80.79000000000001</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -5943,31 +5943,31 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>55844</v>
+        <v>55488.1</v>
       </c>
       <c r="D53" t="n">
         <v>55488.1</v>
       </c>
       <c r="E53" t="n">
-        <v>355.9</v>
+        <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>55989.55</v>
+        <v>55883.7</v>
       </c>
       <c r="G53" t="n">
         <v>55804.16</v>
       </c>
       <c r="H53" t="n">
-        <v>185.39</v>
+        <v>79.54000000000001</v>
       </c>
       <c r="I53" t="n">
-        <v>55526.3</v>
+        <v>55331.1</v>
       </c>
       <c r="J53" t="n">
         <v>55251.56</v>
       </c>
       <c r="K53" t="n">
-        <v>274.74</v>
+        <v>79.54000000000001</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
@@ -5980,7 +5980,7 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>0.64</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N53"/>
+  <dimension ref="A1:N54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3190,6 +3190,58 @@
         </is>
       </c>
       <c r="N53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>22811.35</v>
+      </c>
+      <c r="D54" t="n">
+        <v>22811.35</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" t="n">
+        <v>23120.9</v>
+      </c>
+      <c r="G54" t="n">
+        <v>23071.54</v>
+      </c>
+      <c r="H54" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="I54" t="n">
+        <v>22649.9</v>
+      </c>
+      <c r="J54" t="n">
+        <v>22600.54</v>
+      </c>
+      <c r="K54" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N54" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3204,7 +3256,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N53"/>
+  <dimension ref="A1:N54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5983,6 +6035,58 @@
         <v>0</v>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>54976.9</v>
+      </c>
+      <c r="D54" t="n">
+        <v>54976.9</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" t="n">
+        <v>55867.45</v>
+      </c>
+      <c r="G54" t="n">
+        <v>55664.09</v>
+      </c>
+      <c r="H54" t="n">
+        <v>203.36</v>
+      </c>
+      <c r="I54" t="n">
+        <v>54696.45</v>
+      </c>
+      <c r="J54" t="n">
+        <v>54493.09</v>
+      </c>
+      <c r="K54" t="n">
+        <v>203.36</v>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N54" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -3205,31 +3205,31 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>22811.35</v>
+        <v>22888.95</v>
       </c>
       <c r="D54" t="n">
         <v>22811.35</v>
       </c>
       <c r="E54" t="n">
-        <v>0</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="F54" t="n">
-        <v>23120.9</v>
+        <v>23175.25</v>
       </c>
       <c r="G54" t="n">
         <v>23071.54</v>
       </c>
       <c r="H54" t="n">
-        <v>49.36</v>
+        <v>103.71</v>
       </c>
       <c r="I54" t="n">
-        <v>22649.9</v>
+        <v>22845</v>
       </c>
       <c r="J54" t="n">
         <v>22600.54</v>
       </c>
       <c r="K54" t="n">
-        <v>49.36</v>
+        <v>244.46</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>0.34</v>
       </c>
     </row>
   </sheetData>
@@ -6047,31 +6047,31 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>54976.9</v>
+        <v>55488.1</v>
       </c>
       <c r="D54" t="n">
         <v>54976.9</v>
       </c>
       <c r="E54" t="n">
-        <v>0</v>
+        <v>511.2</v>
       </c>
       <c r="F54" t="n">
-        <v>55867.45</v>
+        <v>55883.7</v>
       </c>
       <c r="G54" t="n">
         <v>55664.09</v>
       </c>
       <c r="H54" t="n">
-        <v>203.36</v>
+        <v>219.61</v>
       </c>
       <c r="I54" t="n">
-        <v>54696.45</v>
+        <v>55331.1</v>
       </c>
       <c r="J54" t="n">
         <v>54493.09</v>
       </c>
       <c r="K54" t="n">
-        <v>203.36</v>
+        <v>838.01</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>0.93</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N54"/>
+  <dimension ref="A1:N55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3243,6 +3243,58 @@
       </c>
       <c r="N54" t="n">
         <v>0.34</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>22687.65</v>
+      </c>
+      <c r="D55" t="n">
+        <v>22687.65</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" t="n">
+        <v>22784.7</v>
+      </c>
+      <c r="G55" t="n">
+        <v>22796.61</v>
+      </c>
+      <c r="H55" t="n">
+        <v>-11.91</v>
+      </c>
+      <c r="I55" t="n">
+        <v>22554.85</v>
+      </c>
+      <c r="J55" t="n">
+        <v>22566.76</v>
+      </c>
+      <c r="K55" t="n">
+        <v>-11.91</v>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N55" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3256,7 +3308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N54"/>
+  <dimension ref="A1:N55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6087,6 +6139,58 @@
         <v>0.93</v>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>54925.7</v>
+      </c>
+      <c r="D55" t="n">
+        <v>54925.7</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" t="n">
+        <v>55134.45</v>
+      </c>
+      <c r="G55" t="n">
+        <v>55220.31</v>
+      </c>
+      <c r="H55" t="n">
+        <v>-85.86</v>
+      </c>
+      <c r="I55" t="n">
+        <v>54459.35</v>
+      </c>
+      <c r="J55" t="n">
+        <v>54545.21</v>
+      </c>
+      <c r="K55" t="n">
+        <v>-85.86</v>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N55" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -3257,31 +3257,31 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>22687.65</v>
+        <v>22811.35</v>
       </c>
       <c r="D55" t="n">
         <v>22687.65</v>
       </c>
       <c r="E55" t="n">
-        <v>0</v>
+        <v>123.7</v>
       </c>
       <c r="F55" t="n">
-        <v>22784.7</v>
+        <v>23120.9</v>
       </c>
       <c r="G55" t="n">
         <v>22796.61</v>
       </c>
       <c r="H55" t="n">
-        <v>-11.91</v>
+        <v>324.29</v>
       </c>
       <c r="I55" t="n">
-        <v>22554.85</v>
+        <v>22649.9</v>
       </c>
       <c r="J55" t="n">
         <v>22566.76</v>
       </c>
       <c r="K55" t="n">
-        <v>-11.91</v>
+        <v>83.14</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>0.55</v>
       </c>
     </row>
   </sheetData>
@@ -6151,31 +6151,31 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>54925.7</v>
+        <v>54976.9</v>
       </c>
       <c r="D55" t="n">
         <v>54925.7</v>
       </c>
       <c r="E55" t="n">
-        <v>0</v>
+        <v>51.2</v>
       </c>
       <c r="F55" t="n">
-        <v>55134.45</v>
+        <v>55867.45</v>
       </c>
       <c r="G55" t="n">
         <v>55220.31</v>
       </c>
       <c r="H55" t="n">
-        <v>-85.86</v>
+        <v>647.14</v>
       </c>
       <c r="I55" t="n">
-        <v>54459.35</v>
+        <v>54696.45</v>
       </c>
       <c r="J55" t="n">
         <v>54545.21</v>
       </c>
       <c r="K55" t="n">
-        <v>-85.86</v>
+        <v>151.24</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
@@ -6188,7 +6188,7 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N55"/>
+  <dimension ref="A1:N56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3295,6 +3295,58 @@
       </c>
       <c r="N55" t="n">
         <v>0.55</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>22600</v>
+      </c>
+      <c r="D56" t="n">
+        <v>22600</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" t="n">
+        <v>22787.25</v>
+      </c>
+      <c r="G56" t="n">
+        <v>22800.84</v>
+      </c>
+      <c r="H56" t="n">
+        <v>-13.59</v>
+      </c>
+      <c r="I56" t="n">
+        <v>22372</v>
+      </c>
+      <c r="J56" t="n">
+        <v>22385.59</v>
+      </c>
+      <c r="K56" t="n">
+        <v>-13.59</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N56" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3308,7 +3360,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N55"/>
+  <dimension ref="A1:N56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6191,6 +6243,58 @@
         <v>0.09</v>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>54287.35</v>
+      </c>
+      <c r="D56" t="n">
+        <v>54287.35</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" t="n">
+        <v>54990.5</v>
+      </c>
+      <c r="G56" t="n">
+        <v>54871.11</v>
+      </c>
+      <c r="H56" t="n">
+        <v>119.39</v>
+      </c>
+      <c r="I56" t="n">
+        <v>53942.35</v>
+      </c>
+      <c r="J56" t="n">
+        <v>53822.96</v>
+      </c>
+      <c r="K56" t="n">
+        <v>119.39</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N56" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -3309,31 +3309,31 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>22600</v>
+        <v>22687.65</v>
       </c>
       <c r="D56" t="n">
         <v>22600</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>87.65000000000001</v>
       </c>
       <c r="F56" t="n">
-        <v>22787.25</v>
+        <v>22785</v>
       </c>
       <c r="G56" t="n">
         <v>22800.84</v>
       </c>
       <c r="H56" t="n">
-        <v>-13.59</v>
+        <v>-15.84</v>
       </c>
       <c r="I56" t="n">
-        <v>22372</v>
+        <v>22554.85</v>
       </c>
       <c r="J56" t="n">
         <v>22385.59</v>
       </c>
       <c r="K56" t="n">
-        <v>-13.59</v>
+        <v>169.26</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>0.39</v>
       </c>
     </row>
   </sheetData>
@@ -6255,31 +6255,31 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>54287.35</v>
+        <v>54925.7</v>
       </c>
       <c r="D56" t="n">
         <v>54287.35</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>638.35</v>
       </c>
       <c r="F56" t="n">
-        <v>54990.5</v>
+        <v>55134.45</v>
       </c>
       <c r="G56" t="n">
         <v>54871.11</v>
       </c>
       <c r="H56" t="n">
-        <v>119.39</v>
+        <v>263.34</v>
       </c>
       <c r="I56" t="n">
-        <v>53942.35</v>
+        <v>54459.35</v>
       </c>
       <c r="J56" t="n">
         <v>53822.96</v>
       </c>
       <c r="K56" t="n">
-        <v>119.39</v>
+        <v>636.39</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
@@ -6292,7 +6292,7 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -3309,31 +3309,31 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>22687.65</v>
+        <v>22600</v>
       </c>
       <c r="D56" t="n">
         <v>22600</v>
       </c>
       <c r="E56" t="n">
-        <v>87.65000000000001</v>
+        <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>22785</v>
+        <v>22787.25</v>
       </c>
       <c r="G56" t="n">
         <v>22800.84</v>
       </c>
       <c r="H56" t="n">
-        <v>-15.84</v>
+        <v>-13.59</v>
       </c>
       <c r="I56" t="n">
-        <v>22554.85</v>
+        <v>22372</v>
       </c>
       <c r="J56" t="n">
         <v>22385.59</v>
       </c>
       <c r="K56" t="n">
-        <v>169.26</v>
+        <v>-13.59</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>0.39</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -6255,31 +6255,31 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>54925.7</v>
+        <v>54287.35</v>
       </c>
       <c r="D56" t="n">
         <v>54287.35</v>
       </c>
       <c r="E56" t="n">
-        <v>638.35</v>
+        <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>55134.45</v>
+        <v>54990.5</v>
       </c>
       <c r="G56" t="n">
         <v>54871.11</v>
       </c>
       <c r="H56" t="n">
-        <v>263.34</v>
+        <v>119.39</v>
       </c>
       <c r="I56" t="n">
-        <v>54459.35</v>
+        <v>53942.35</v>
       </c>
       <c r="J56" t="n">
         <v>53822.96</v>
       </c>
       <c r="K56" t="n">
-        <v>636.39</v>
+        <v>119.39</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
@@ -6292,7 +6292,7 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N56"/>
+  <dimension ref="A1:N57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3346,6 +3346,58 @@
         </is>
       </c>
       <c r="N56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>22753.2</v>
+      </c>
+      <c r="D57" t="n">
+        <v>22753.2</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" t="n">
+        <v>22753.2</v>
+      </c>
+      <c r="G57" t="n">
+        <v>22875.15</v>
+      </c>
+      <c r="H57" t="n">
+        <v>-121.95</v>
+      </c>
+      <c r="I57" t="n">
+        <v>22387.35</v>
+      </c>
+      <c r="J57" t="n">
+        <v>22509.3</v>
+      </c>
+      <c r="K57" t="n">
+        <v>-121.95</v>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N57" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3360,7 +3412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N56"/>
+  <dimension ref="A1:N57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6295,6 +6347,58 @@
         <v>0</v>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>54366.7</v>
+      </c>
+      <c r="D57" t="n">
+        <v>54366.7</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" t="n">
+        <v>54392.5</v>
+      </c>
+      <c r="G57" t="n">
+        <v>54580.3</v>
+      </c>
+      <c r="H57" t="n">
+        <v>-187.8</v>
+      </c>
+      <c r="I57" t="n">
+        <v>53777.5</v>
+      </c>
+      <c r="J57" t="n">
+        <v>53965.3</v>
+      </c>
+      <c r="K57" t="n">
+        <v>-187.8</v>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N57" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -3361,31 +3361,31 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>22753.2</v>
+        <v>22600</v>
       </c>
       <c r="D57" t="n">
         <v>22753.2</v>
       </c>
       <c r="E57" t="n">
-        <v>0</v>
+        <v>-153.2</v>
       </c>
       <c r="F57" t="n">
-        <v>22753.2</v>
+        <v>22787.25</v>
       </c>
       <c r="G57" t="n">
         <v>22875.15</v>
       </c>
       <c r="H57" t="n">
-        <v>-121.95</v>
+        <v>-87.90000000000001</v>
       </c>
       <c r="I57" t="n">
-        <v>22387.35</v>
+        <v>22372</v>
       </c>
       <c r="J57" t="n">
         <v>22509.3</v>
       </c>
       <c r="K57" t="n">
-        <v>-121.95</v>
+        <v>-137.3</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
@@ -3398,7 +3398,7 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
     </row>
   </sheetData>
@@ -6359,31 +6359,31 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>54366.7</v>
+        <v>54287.35</v>
       </c>
       <c r="D57" t="n">
         <v>54366.7</v>
       </c>
       <c r="E57" t="n">
-        <v>0</v>
+        <v>-79.34999999999999</v>
       </c>
       <c r="F57" t="n">
-        <v>54392.5</v>
+        <v>54990.5</v>
       </c>
       <c r="G57" t="n">
         <v>54580.3</v>
       </c>
       <c r="H57" t="n">
-        <v>-187.8</v>
+        <v>410.2</v>
       </c>
       <c r="I57" t="n">
-        <v>53777.5</v>
+        <v>53942.35</v>
       </c>
       <c r="J57" t="n">
         <v>53965.3</v>
       </c>
       <c r="K57" t="n">
-        <v>-187.8</v>
+        <v>-22.95</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
@@ -6396,7 +6396,7 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N57"/>
+  <dimension ref="A1:N58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3399,6 +3399,58 @@
       </c>
       <c r="N57" t="n">
         <v>0.67</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>22749.75</v>
+      </c>
+      <c r="D58" t="n">
+        <v>22749.75</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" t="n">
+        <v>22829.75</v>
+      </c>
+      <c r="G58" t="n">
+        <v>22840.71</v>
+      </c>
+      <c r="H58" t="n">
+        <v>-10.96</v>
+      </c>
+      <c r="I58" t="n">
+        <v>22636.85</v>
+      </c>
+      <c r="J58" t="n">
+        <v>22647.81</v>
+      </c>
+      <c r="K58" t="n">
+        <v>-10.96</v>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N58" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3412,7 +3464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N57"/>
+  <dimension ref="A1:N58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6399,6 +6451,58 @@
         <v>0.15</v>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>53974.9</v>
+      </c>
+      <c r="D58" t="n">
+        <v>53974.9</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" t="n">
+        <v>54654.05</v>
+      </c>
+      <c r="G58" t="n">
+        <v>54435.56</v>
+      </c>
+      <c r="H58" t="n">
+        <v>218.49</v>
+      </c>
+      <c r="I58" t="n">
+        <v>53951.2</v>
+      </c>
+      <c r="J58" t="n">
+        <v>53732.71</v>
+      </c>
+      <c r="K58" t="n">
+        <v>218.49</v>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N58" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -3413,31 +3413,31 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>22749.75</v>
+        <v>22753.2</v>
       </c>
       <c r="D58" t="n">
         <v>22749.75</v>
       </c>
       <c r="E58" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="F58" t="n">
-        <v>22829.75</v>
+        <v>22753.2</v>
       </c>
       <c r="G58" t="n">
         <v>22840.71</v>
       </c>
       <c r="H58" t="n">
-        <v>-10.96</v>
+        <v>-87.51000000000001</v>
       </c>
       <c r="I58" t="n">
-        <v>22636.85</v>
+        <v>22387.35</v>
       </c>
       <c r="J58" t="n">
         <v>22647.81</v>
       </c>
       <c r="K58" t="n">
-        <v>-10.96</v>
+        <v>-260.46</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
     </row>
   </sheetData>
@@ -6463,31 +6463,31 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>53974.9</v>
+        <v>54366.7</v>
       </c>
       <c r="D58" t="n">
         <v>53974.9</v>
       </c>
       <c r="E58" t="n">
-        <v>0</v>
+        <v>391.8</v>
       </c>
       <c r="F58" t="n">
-        <v>54654.05</v>
+        <v>54392.5</v>
       </c>
       <c r="G58" t="n">
         <v>54435.56</v>
       </c>
       <c r="H58" t="n">
-        <v>218.49</v>
+        <v>-43.06</v>
       </c>
       <c r="I58" t="n">
-        <v>53951.2</v>
+        <v>53777.5</v>
       </c>
       <c r="J58" t="n">
         <v>53732.71</v>
       </c>
       <c r="K58" t="n">
-        <v>218.49</v>
+        <v>44.79</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
@@ -6500,7 +6500,7 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>0.73</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N58"/>
+  <dimension ref="A1:N59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3451,6 +3451,58 @@
       </c>
       <c r="N58" t="n">
         <v>0.02</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>22698.85</v>
+      </c>
+      <c r="D59" t="n">
+        <v>22698.85</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" t="n">
+        <v>22778.05</v>
+      </c>
+      <c r="G59" t="n">
+        <v>22818.7</v>
+      </c>
+      <c r="H59" t="n">
+        <v>-40.65</v>
+      </c>
+      <c r="I59" t="n">
+        <v>22497.7</v>
+      </c>
+      <c r="J59" t="n">
+        <v>22538.35</v>
+      </c>
+      <c r="K59" t="n">
+        <v>-40.65</v>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N59" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3464,7 +3516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N58"/>
+  <dimension ref="A1:N59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6503,6 +6555,58 @@
         <v>0.73</v>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>54267.4</v>
+      </c>
+      <c r="D59" t="n">
+        <v>54267.4</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" t="n">
+        <v>54440.25</v>
+      </c>
+      <c r="G59" t="n">
+        <v>54596.39</v>
+      </c>
+      <c r="H59" t="n">
+        <v>-156.14</v>
+      </c>
+      <c r="I59" t="n">
+        <v>53626.15</v>
+      </c>
+      <c r="J59" t="n">
+        <v>53782.29</v>
+      </c>
+      <c r="K59" t="n">
+        <v>-156.14</v>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N59" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -3465,31 +3465,31 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>22698.85</v>
+        <v>22749.75</v>
       </c>
       <c r="D59" t="n">
         <v>22698.85</v>
       </c>
       <c r="E59" t="n">
-        <v>0</v>
+        <v>50.9</v>
       </c>
       <c r="F59" t="n">
-        <v>22778.05</v>
+        <v>22829.75</v>
       </c>
       <c r="G59" t="n">
         <v>22818.7</v>
       </c>
       <c r="H59" t="n">
-        <v>-40.65</v>
+        <v>11.05</v>
       </c>
       <c r="I59" t="n">
-        <v>22497.7</v>
+        <v>22636.85</v>
       </c>
       <c r="J59" t="n">
         <v>22538.35</v>
       </c>
       <c r="K59" t="n">
-        <v>-40.65</v>
+        <v>98.5</v>
       </c>
       <c r="L59" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
     </row>
   </sheetData>
@@ -6567,31 +6567,31 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>54267.4</v>
+        <v>53974.9</v>
       </c>
       <c r="D59" t="n">
         <v>54267.4</v>
       </c>
       <c r="E59" t="n">
-        <v>0</v>
+        <v>-292.5</v>
       </c>
       <c r="F59" t="n">
-        <v>54440.25</v>
+        <v>54654.05</v>
       </c>
       <c r="G59" t="n">
         <v>54596.39</v>
       </c>
       <c r="H59" t="n">
-        <v>-156.14</v>
+        <v>57.66</v>
       </c>
       <c r="I59" t="n">
-        <v>53626.15</v>
+        <v>53951.2</v>
       </c>
       <c r="J59" t="n">
         <v>53782.29</v>
       </c>
       <c r="K59" t="n">
-        <v>-156.14</v>
+        <v>168.91</v>
       </c>
       <c r="L59" t="inlineStr">
         <is>
@@ -6604,7 +6604,7 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>0.54</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N59"/>
+  <dimension ref="A1:N60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3503,6 +3503,58 @@
       </c>
       <c r="N59" t="n">
         <v>0.22</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>22936.75</v>
+      </c>
+      <c r="D60" t="n">
+        <v>22936.75</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" t="n">
+        <v>22961.95</v>
+      </c>
+      <c r="G60" t="n">
+        <v>23046.89</v>
+      </c>
+      <c r="H60" t="n">
+        <v>-84.94</v>
+      </c>
+      <c r="I60" t="n">
+        <v>22656.75</v>
+      </c>
+      <c r="J60" t="n">
+        <v>22741.69</v>
+      </c>
+      <c r="K60" t="n">
+        <v>-84.94</v>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N60" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3516,7 +3568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N59"/>
+  <dimension ref="A1:N60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6607,6 +6659,58 @@
         <v>0.54</v>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>54909.65</v>
+      </c>
+      <c r="D60" t="n">
+        <v>54909.65</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" t="n">
+        <v>54980.15</v>
+      </c>
+      <c r="G60" t="n">
+        <v>55243.9</v>
+      </c>
+      <c r="H60" t="n">
+        <v>-263.75</v>
+      </c>
+      <c r="I60" t="n">
+        <v>54047.9</v>
+      </c>
+      <c r="J60" t="n">
+        <v>54311.65</v>
+      </c>
+      <c r="K60" t="n">
+        <v>-263.75</v>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N60" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -3517,31 +3517,31 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>22936.75</v>
+        <v>22698.85</v>
       </c>
       <c r="D60" t="n">
         <v>22936.75</v>
       </c>
       <c r="E60" t="n">
-        <v>0</v>
+        <v>-237.9</v>
       </c>
       <c r="F60" t="n">
-        <v>22961.95</v>
+        <v>22778.05</v>
       </c>
       <c r="G60" t="n">
         <v>23046.89</v>
       </c>
       <c r="H60" t="n">
-        <v>-84.94</v>
+        <v>-268.84</v>
       </c>
       <c r="I60" t="n">
-        <v>22656.75</v>
+        <v>22497.7</v>
       </c>
       <c r="J60" t="n">
         <v>22741.69</v>
       </c>
       <c r="K60" t="n">
-        <v>-84.94</v>
+        <v>-243.99</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
@@ -3554,7 +3554,7 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
     </row>
   </sheetData>
@@ -6671,31 +6671,31 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>54909.65</v>
+        <v>54267.4</v>
       </c>
       <c r="D60" t="n">
         <v>54909.65</v>
       </c>
       <c r="E60" t="n">
-        <v>0</v>
+        <v>-642.25</v>
       </c>
       <c r="F60" t="n">
-        <v>54980.15</v>
+        <v>54440.25</v>
       </c>
       <c r="G60" t="n">
         <v>55243.9</v>
       </c>
       <c r="H60" t="n">
-        <v>-263.75</v>
+        <v>-803.65</v>
       </c>
       <c r="I60" t="n">
-        <v>54047.9</v>
+        <v>53626.15</v>
       </c>
       <c r="J60" t="n">
         <v>54311.65</v>
       </c>
       <c r="K60" t="n">
-        <v>-263.75</v>
+        <v>-685.5</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
@@ -6708,7 +6708,7 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N60"/>
+  <dimension ref="A1:N61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3555,6 +3555,58 @@
       </c>
       <c r="N60" t="n">
         <v>1.04</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>23053.1</v>
+      </c>
+      <c r="D61" t="n">
+        <v>23053.1</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" t="n">
+        <v>23118.1</v>
+      </c>
+      <c r="G61" t="n">
+        <v>23145.76</v>
+      </c>
+      <c r="H61" t="n">
+        <v>-27.66</v>
+      </c>
+      <c r="I61" t="n">
+        <v>22905.1</v>
+      </c>
+      <c r="J61" t="n">
+        <v>22932.76</v>
+      </c>
+      <c r="K61" t="n">
+        <v>-27.66</v>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N61" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3568,7 +3620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N60"/>
+  <dimension ref="A1:N61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6711,6 +6763,58 @@
         <v>1.17</v>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>54686.95</v>
+      </c>
+      <c r="D61" t="n">
+        <v>54686.95</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" t="n">
+        <v>55068.5</v>
+      </c>
+      <c r="G61" t="n">
+        <v>54976.71</v>
+      </c>
+      <c r="H61" t="n">
+        <v>91.79000000000001</v>
+      </c>
+      <c r="I61" t="n">
+        <v>54580.75</v>
+      </c>
+      <c r="J61" t="n">
+        <v>54488.96</v>
+      </c>
+      <c r="K61" t="n">
+        <v>91.79000000000001</v>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N61" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -3569,31 +3569,31 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>23053.1</v>
+        <v>22936.75</v>
       </c>
       <c r="D61" t="n">
         <v>23053.1</v>
       </c>
       <c r="E61" t="n">
-        <v>0</v>
+        <v>-116.35</v>
       </c>
       <c r="F61" t="n">
-        <v>23118.1</v>
+        <v>22961.95</v>
       </c>
       <c r="G61" t="n">
         <v>23145.76</v>
       </c>
       <c r="H61" t="n">
-        <v>-27.66</v>
+        <v>-183.81</v>
       </c>
       <c r="I61" t="n">
-        <v>22905.1</v>
+        <v>22656.75</v>
       </c>
       <c r="J61" t="n">
         <v>22932.76</v>
       </c>
       <c r="K61" t="n">
-        <v>-27.66</v>
+        <v>-276.01</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
@@ -6775,31 +6775,31 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>54686.95</v>
+        <v>54909.65</v>
       </c>
       <c r="D61" t="n">
         <v>54686.95</v>
       </c>
       <c r="E61" t="n">
-        <v>0</v>
+        <v>222.7</v>
       </c>
       <c r="F61" t="n">
-        <v>55068.5</v>
+        <v>54980.15</v>
       </c>
       <c r="G61" t="n">
         <v>54976.71</v>
       </c>
       <c r="H61" t="n">
-        <v>91.79000000000001</v>
+        <v>3.44</v>
       </c>
       <c r="I61" t="n">
-        <v>54580.75</v>
+        <v>54047.9</v>
       </c>
       <c r="J61" t="n">
         <v>54488.96</v>
       </c>
       <c r="K61" t="n">
-        <v>91.79000000000001</v>
+        <v>-441.06</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
@@ -6812,7 +6812,7 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>0.41</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -3569,31 +3569,31 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>22936.75</v>
+        <v>23053.1</v>
       </c>
       <c r="D61" t="n">
         <v>23053.1</v>
       </c>
       <c r="E61" t="n">
-        <v>-116.35</v>
+        <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>22961.95</v>
+        <v>23118.1</v>
       </c>
       <c r="G61" t="n">
         <v>23145.76</v>
       </c>
       <c r="H61" t="n">
-        <v>-183.81</v>
+        <v>-27.66</v>
       </c>
       <c r="I61" t="n">
-        <v>22656.75</v>
+        <v>22905.1</v>
       </c>
       <c r="J61" t="n">
         <v>22932.76</v>
       </c>
       <c r="K61" t="n">
-        <v>-276.01</v>
+        <v>-27.66</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -6775,31 +6775,31 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>54909.65</v>
+        <v>54686.95</v>
       </c>
       <c r="D61" t="n">
         <v>54686.95</v>
       </c>
       <c r="E61" t="n">
-        <v>222.7</v>
+        <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>54980.15</v>
+        <v>55068.5</v>
       </c>
       <c r="G61" t="n">
         <v>54976.71</v>
       </c>
       <c r="H61" t="n">
-        <v>3.44</v>
+        <v>91.79000000000001</v>
       </c>
       <c r="I61" t="n">
-        <v>54047.9</v>
+        <v>54580.75</v>
       </c>
       <c r="J61" t="n">
         <v>54488.96</v>
       </c>
       <c r="K61" t="n">
-        <v>-441.06</v>
+        <v>91.79000000000001</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
@@ -6812,7 +6812,7 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>0.41</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
